--- a/output/2026-10-15/enriched_analysis.xlsx
+++ b/output/2026-10-15/enriched_analysis.xlsx
@@ -929,13 +929,13 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>2.215</v>
+        <v>2.283</v>
       </c>
       <c r="W2" t="n">
-        <v>2844</v>
+        <v>2760</v>
       </c>
       <c r="X2" t="n">
-        <v>22.3</v>
+        <v>21.6</v>
       </c>
       <c r="Y2" t="n">
         <v>75</v>
@@ -1161,13 +1161,13 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>0.824</v>
+        <v>0.819</v>
       </c>
       <c r="W3" t="n">
-        <v>982</v>
+        <v>988</v>
       </c>
       <c r="X3" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="Y3" t="n">
         <v>47</v>
@@ -1396,10 +1396,10 @@
         <v>0.021</v>
       </c>
       <c r="W4" t="n">
-        <v>3493</v>
+        <v>3464</v>
       </c>
       <c r="X4" t="n">
-        <v>15.8</v>
+        <v>15.7</v>
       </c>
       <c r="Y4" t="n">
         <v>18</v>
@@ -1625,13 +1625,13 @@
         </is>
       </c>
       <c r="V5" t="n">
-        <v>0.044</v>
+        <v>0.045</v>
       </c>
       <c r="W5" t="n">
-        <v>3044</v>
+        <v>2953</v>
       </c>
       <c r="X5" t="n">
-        <v>10.5</v>
+        <v>10.2</v>
       </c>
       <c r="Y5" t="n">
         <v>36</v>
@@ -1857,10 +1857,10 @@
         </is>
       </c>
       <c r="V6" t="n">
-        <v>1.922</v>
+        <v>1.894</v>
       </c>
       <c r="W6" t="n">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="V7" t="n">
-        <v>1.033</v>
+        <v>1.039</v>
       </c>
       <c r="W7" t="n">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="X7" t="n">
-        <v>87.5</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="Y7" t="n">
         <v>111</v>
@@ -2319,13 +2319,13 @@
         </is>
       </c>
       <c r="V8" t="n">
-        <v>0.239</v>
+        <v>0.24</v>
       </c>
       <c r="W8" t="n">
-        <v>1443</v>
+        <v>1433</v>
       </c>
       <c r="X8" t="n">
-        <v>24.5</v>
+        <v>24.4</v>
       </c>
       <c r="Y8" t="n">
         <v>8</v>
@@ -2549,13 +2549,13 @@
         </is>
       </c>
       <c r="V9" t="n">
-        <v>0.124</v>
+        <v>0.127</v>
       </c>
       <c r="W9" t="n">
-        <v>703</v>
+        <v>687</v>
       </c>
       <c r="X9" t="n">
-        <v>26.5</v>
+        <v>26</v>
       </c>
       <c r="Y9" t="n">
         <v>13</v>
@@ -2709,16 +2709,16 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BMWVENTLTD</t>
+          <t>NURECA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BMW VENTURES LIMITED</t>
+          <t>NURECA LIMITED</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2726,40 +2726,40 @@
         </is>
       </c>
       <c r="E10" t="n">
+        <v>17</v>
+      </c>
+      <c r="F10" t="n">
         <v>10</v>
       </c>
-      <c r="F10" t="n">
-        <v>19</v>
-      </c>
       <c r="G10" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="H10" t="n">
         <v>-1</v>
       </c>
       <c r="I10" t="n">
-        <v>65.48</v>
+        <v>323.35</v>
       </c>
       <c r="J10" t="n">
-        <v>55.06</v>
+        <v>333.11</v>
       </c>
       <c r="K10" t="n">
-        <v>18.9</v>
+        <v>-2.9</v>
       </c>
       <c r="L10" t="n">
-        <v>73.01000000000001</v>
+        <v>63.24</v>
       </c>
       <c r="M10" t="n">
-        <v>2.9</v>
+        <v>3.75</v>
       </c>
       <c r="N10" t="n">
-        <v>28991535</v>
+        <v>37538354</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>28991535</v>
+        <v>37538354</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2773,163 +2773,163 @@
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>22-09-2026</t>
+          <t>30-09-2026</t>
         </is>
       </c>
       <c r="V10" t="n">
-        <v>0.51</v>
+        <v>1.207</v>
       </c>
       <c r="W10" t="n">
-        <v>568</v>
+        <v>311</v>
       </c>
       <c r="X10" t="n">
-        <v>14.2</v>
+        <v>143</v>
       </c>
       <c r="Y10" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>264</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>6.06</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>333.07</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>285.05</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>333.1146252074293</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>-2.9</v>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Confirmed Accumulation</t>
+        </is>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>Confirmed Accumulation</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>24-07-2026</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>30-09-2026</t>
+        </is>
+      </c>
+      <c r="AQ10" t="n">
+        <v>68</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>83</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>15</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW10" t="n">
         <v>19</v>
       </c>
-      <c r="Z10" t="n">
-        <v>21</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>20</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>12</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="AE10" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>55.44</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>57.72</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>55.06464387464388</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="AL10" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Confirmed Accumulation</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>Mature — Wait for Pullback</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>05-08-2026</t>
-        </is>
-      </c>
-      <c r="AP10" t="inlineStr">
-        <is>
-          <t>22-09-2026</t>
-        </is>
-      </c>
-      <c r="AQ10" t="n">
-        <v>48</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>71</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>23</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV10" t="n">
+      <c r="AX10" t="n">
+        <v>26</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>19454866</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>23414636</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>37538354</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>19454866</v>
+      </c>
+      <c r="BP10" t="n">
         <v>3</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>3</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>6</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>10009832</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>10009832</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>28991535</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO10" t="n">
-        <v>10009832</v>
-      </c>
-      <c r="BP10" t="n">
-        <v>1</v>
       </c>
       <c r="BQ10" t="n">
         <v>0</v>
@@ -2941,12 +2941,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>NURECA</t>
+          <t>SRHHYPOLTD</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NURECA LIMITED</t>
+          <t>Sree Rayalaseema Hi-Strength Hypo Limited</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -2958,107 +2958,107 @@
         </is>
       </c>
       <c r="E11" t="n">
+        <v>9</v>
+      </c>
+      <c r="F11" t="n">
+        <v>12</v>
+      </c>
+      <c r="G11" t="n">
+        <v>25</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>550.6</v>
+      </c>
+      <c r="J11" t="n">
+        <v>510.94</v>
+      </c>
+      <c r="K11" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="L11" t="n">
+        <v>61.84</v>
+      </c>
+      <c r="M11" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="N11" t="n">
+        <v>30622049</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>30622049</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>Net Buying</t>
+        </is>
+      </c>
+      <c r="S11" t="b">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
         <v>17</v>
       </c>
-      <c r="F11" t="n">
-        <v>10</v>
-      </c>
-      <c r="G11" t="n">
-        <v>13</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-1</v>
-      </c>
-      <c r="I11" t="n">
-        <v>323.35</v>
-      </c>
-      <c r="J11" t="n">
-        <v>333.11</v>
-      </c>
-      <c r="K11" t="n">
-        <v>-2.9</v>
-      </c>
-      <c r="L11" t="n">
-        <v>63.24</v>
-      </c>
-      <c r="M11" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="N11" t="n">
-        <v>37538354</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>37538354</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>Net Buying</t>
-        </is>
-      </c>
-      <c r="S11" t="b">
-        <v>0</v>
-      </c>
-      <c r="T11" t="n">
-        <v>26</v>
-      </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>21-09-2026</t>
         </is>
       </c>
       <c r="V11" t="n">
-        <v>1.215</v>
+        <v>0.333</v>
       </c>
       <c r="W11" t="n">
-        <v>309</v>
+        <v>919</v>
       </c>
       <c r="X11" t="n">
-        <v>142</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="Y11" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.45</v>
+        <v>30</v>
       </c>
       <c r="AA11" t="n">
-        <v>264</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.55</v>
+        <v>14.66</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.07</v>
+        <v>14.1</v>
       </c>
       <c r="AD11" t="n">
         <v>0.01</v>
       </c>
       <c r="AE11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF11" t="n">
-        <v>6.06</v>
+        <v>14</v>
       </c>
       <c r="AG11" t="n">
-        <v>333.07</v>
+        <v>521.75</v>
       </c>
       <c r="AH11" t="n">
-        <v>285.05</v>
+        <v>492.74</v>
       </c>
       <c r="AI11" t="n">
-        <v>27.1</v>
+        <v>19.3</v>
       </c>
       <c r="AJ11" t="n">
-        <v>333.1146252074293</v>
+        <v>510.9380308010612</v>
       </c>
       <c r="AK11" t="n">
-        <v>-2.9</v>
+        <v>7.8</v>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
@@ -3077,22 +3077,22 @@
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>24-07-2026</t>
+          <t>26-08-2026</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>21-09-2026</t>
         </is>
       </c>
       <c r="AQ11" t="n">
-        <v>68</v>
+        <v>26</v>
       </c>
       <c r="AR11" t="n">
-        <v>83</v>
+        <v>50</v>
       </c>
       <c r="AS11" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="AT11" t="n">
         <v>0</v>
@@ -3101,13 +3101,13 @@
         <v>0</v>
       </c>
       <c r="AV11" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="AW11" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AX11" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="AY11" t="n">
         <v>0</v>
@@ -3116,13 +3116,13 @@
         <v>0</v>
       </c>
       <c r="BA11" t="n">
-        <v>19454866</v>
+        <v>9018372</v>
       </c>
       <c r="BB11" t="n">
-        <v>23414636</v>
+        <v>30622049</v>
       </c>
       <c r="BC11" t="n">
-        <v>37538354</v>
+        <v>30622049</v>
       </c>
       <c r="BD11" t="n">
         <v>0</v>
@@ -3158,10 +3158,10 @@
         <v>0</v>
       </c>
       <c r="BO11" t="n">
-        <v>19454866</v>
+        <v>9018372</v>
       </c>
       <c r="BP11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BQ11" t="n">
         <v>0</v>
@@ -3173,12 +3173,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SRHHYPOLTD</t>
+          <t>SIGIND</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Sree Rayalaseema Hi-Strength Hypo Limited</t>
+          <t>Signet Industries Limited</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -3190,40 +3190,40 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F12" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="G12" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>550.6</v>
+        <v>58.31</v>
       </c>
       <c r="J12" t="n">
-        <v>510.94</v>
+        <v>74.22</v>
       </c>
       <c r="K12" t="n">
-        <v>7.8</v>
+        <v>-21.4</v>
       </c>
       <c r="L12" t="n">
-        <v>61.84</v>
+        <v>72.56999999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>3.06</v>
+        <v>2.01</v>
       </c>
       <c r="N12" t="n">
-        <v>30622049</v>
+        <v>20066329</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>30622049</v>
+        <v>20066329</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -3237,60 +3237,60 @@
         <v>0</v>
       </c>
       <c r="T12" t="n">
+        <v>18</v>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>21-09-2026</t>
+        </is>
+      </c>
+      <c r="V12" t="n">
+        <v>1.153</v>
+      </c>
+      <c r="W12" t="n">
+        <v>174</v>
+      </c>
+      <c r="X12" t="n">
+        <v>7.39</v>
+      </c>
+      <c r="Y12" t="n">
         <v>17</v>
       </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>21-09-2026</t>
-        </is>
-      </c>
-      <c r="V12" t="n">
-        <v>0.324</v>
-      </c>
-      <c r="W12" t="n">
-        <v>945</v>
-      </c>
-      <c r="X12" t="n">
-        <v>9.289999999999999</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>7</v>
-      </c>
       <c r="Z12" t="n">
-        <v>30</v>
+        <v>27.97</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AB12" t="n">
-        <v>14.66</v>
+        <v>2.73</v>
       </c>
       <c r="AC12" t="n">
-        <v>14.1</v>
+        <v>13.6</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.01</v>
+        <v>1.86</v>
       </c>
       <c r="AE12" t="b">
         <v>1</v>
       </c>
       <c r="AF12" t="n">
-        <v>14</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="AG12" t="n">
-        <v>521.75</v>
+        <v>67.87</v>
       </c>
       <c r="AH12" t="n">
-        <v>492.74</v>
+        <v>53.47</v>
       </c>
       <c r="AI12" t="n">
-        <v>19.3</v>
+        <v>21</v>
       </c>
       <c r="AJ12" t="n">
-        <v>510.9380308010612</v>
+        <v>74.21830535305453</v>
       </c>
       <c r="AK12" t="n">
-        <v>7.8</v>
+        <v>-21.4</v>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
@@ -3309,7 +3309,7 @@
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>26-08-2026</t>
+          <t>17-08-2026</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
@@ -3318,10 +3318,10 @@
         </is>
       </c>
       <c r="AQ12" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="AR12" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="AS12" t="n">
         <v>24</v>
@@ -3333,13 +3333,13 @@
         <v>0</v>
       </c>
       <c r="AV12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AW12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AX12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AY12" t="n">
         <v>0</v>
@@ -3348,13 +3348,13 @@
         <v>0</v>
       </c>
       <c r="BA12" t="n">
-        <v>9018372</v>
+        <v>1525105</v>
       </c>
       <c r="BB12" t="n">
-        <v>30622049</v>
+        <v>20066329</v>
       </c>
       <c r="BC12" t="n">
-        <v>30622049</v>
+        <v>20066329</v>
       </c>
       <c r="BD12" t="n">
         <v>0</v>
@@ -3390,10 +3390,10 @@
         <v>0</v>
       </c>
       <c r="BO12" t="n">
-        <v>9018372</v>
+        <v>1525105</v>
       </c>
       <c r="BP12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BQ12" t="n">
         <v>0</v>
@@ -3405,16 +3405,16 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SIGIND</t>
+          <t>THANGAMAYL</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Signet Industries Limited</t>
+          <t>THANGAMAYIL JEWELLERY LIMITED</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -3422,10 +3422,10 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="F13" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G13" t="n">
         <v>13</v>
@@ -3434,28 +3434,28 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>58.31</v>
+        <v>4849.5</v>
       </c>
       <c r="J13" t="n">
-        <v>74.22</v>
+        <v>5198.76</v>
       </c>
       <c r="K13" t="n">
-        <v>-21.4</v>
+        <v>-6.7</v>
       </c>
       <c r="L13" t="n">
-        <v>72.56999999999999</v>
+        <v>67.31999999999999</v>
       </c>
       <c r="M13" t="n">
-        <v>2.01</v>
+        <v>7.21</v>
       </c>
       <c r="N13" t="n">
-        <v>20066329</v>
+        <v>72054758</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>20066329</v>
+        <v>72054758</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -3469,94 +3469,94 @@
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>21-09-2026</t>
+          <t>31-08-2026</t>
         </is>
       </c>
       <c r="V13" t="n">
-        <v>1.167</v>
+        <v>0.048</v>
       </c>
       <c r="W13" t="n">
-        <v>172</v>
+        <v>14938</v>
       </c>
       <c r="X13" t="n">
-        <v>7.29</v>
+        <v>38</v>
       </c>
       <c r="Y13" t="n">
-        <v>17</v>
+        <v>83</v>
       </c>
       <c r="Z13" t="n">
-        <v>27.97</v>
+        <v>145</v>
       </c>
       <c r="AA13" t="n">
-        <v>17</v>
+        <v>264</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.73</v>
+        <v>27.38</v>
       </c>
       <c r="AC13" t="n">
-        <v>13.6</v>
+        <v>25.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.86</v>
+        <v>0.64</v>
       </c>
       <c r="AE13" t="b">
         <v>1</v>
       </c>
       <c r="AF13" t="n">
-        <v>9.140000000000001</v>
+        <v>5</v>
       </c>
       <c r="AG13" t="n">
-        <v>67.87</v>
+        <v>5162.65</v>
       </c>
       <c r="AH13" t="n">
-        <v>53.47</v>
+        <v>4556.46</v>
       </c>
       <c r="AI13" t="n">
-        <v>21</v>
+        <v>16.1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>74.21830535305453</v>
+        <v>5198.755988455989</v>
       </c>
       <c r="AK13" t="n">
-        <v>-21.4</v>
+        <v>-6.7</v>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Aging</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Mature Accumulation</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Mature — Wait for Pullback</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>17-08-2026</t>
+          <t>04-08-2026</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>21-09-2026</t>
+          <t>31-08-2026</t>
         </is>
       </c>
       <c r="AQ13" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="AR13" t="n">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="AS13" t="n">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="AT13" t="n">
         <v>0</v>
@@ -3565,13 +3565,13 @@
         <v>0</v>
       </c>
       <c r="AV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW13" t="n">
         <v>2</v>
       </c>
-      <c r="AW13" t="n">
-        <v>18</v>
-      </c>
       <c r="AX13" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="AY13" t="n">
         <v>0</v>
@@ -3580,13 +3580,13 @@
         <v>0</v>
       </c>
       <c r="BA13" t="n">
-        <v>1525105</v>
+        <v>0</v>
       </c>
       <c r="BB13" t="n">
-        <v>20066329</v>
+        <v>19879002</v>
       </c>
       <c r="BC13" t="n">
-        <v>20066329</v>
+        <v>72054758</v>
       </c>
       <c r="BD13" t="n">
         <v>0</v>
@@ -3622,10 +3622,10 @@
         <v>0</v>
       </c>
       <c r="BO13" t="n">
-        <v>1525105</v>
+        <v>0</v>
       </c>
       <c r="BP13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BQ13" t="n">
         <v>0</v>
@@ -3637,12 +3637,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>THANGAMAYL</t>
+          <t>BMWVENTLTD</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>THANGAMAYIL JEWELLERY LIMITED</t>
+          <t>BMW VENTURES LIMITED</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -3654,40 +3654,40 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F14" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="G14" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="I14" t="n">
-        <v>4849.5</v>
+        <v>65.48</v>
       </c>
       <c r="J14" t="n">
-        <v>5198.76</v>
+        <v>55.06</v>
       </c>
       <c r="K14" t="n">
-        <v>-6.7</v>
+        <v>18.9</v>
       </c>
       <c r="L14" t="n">
-        <v>67.31999999999999</v>
+        <v>73.01000000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>7.21</v>
+        <v>2.9</v>
       </c>
       <c r="N14" t="n">
-        <v>72054758</v>
+        <v>28991535</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>72054758</v>
+        <v>28991535</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -3705,65 +3705,65 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>31-08-2026</t>
+          <t>22-09-2026</t>
         </is>
       </c>
       <c r="V14" t="n">
-        <v>0.048</v>
+        <v>0.482</v>
       </c>
       <c r="W14" t="n">
-        <v>15073</v>
+        <v>602</v>
       </c>
       <c r="X14" t="n">
-        <v>38.4</v>
+        <v>15.1</v>
       </c>
       <c r="Y14" t="n">
-        <v>83</v>
+        <v>19</v>
       </c>
       <c r="Z14" t="n">
-        <v>145</v>
+        <v>21</v>
       </c>
       <c r="AA14" t="n">
-        <v>264</v>
+        <v>20</v>
       </c>
       <c r="AB14" t="n">
-        <v>27.38</v>
+        <v>1.22</v>
       </c>
       <c r="AC14" t="n">
-        <v>25.5</v>
+        <v>12</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AE14" t="b">
         <v>1</v>
       </c>
       <c r="AF14" t="n">
-        <v>5</v>
+        <v>3.4</v>
       </c>
       <c r="AG14" t="n">
-        <v>5162.65</v>
+        <v>55.44</v>
       </c>
       <c r="AH14" t="n">
-        <v>4556.46</v>
+        <v>57.72</v>
       </c>
       <c r="AI14" t="n">
-        <v>16.1</v>
+        <v>12.7</v>
       </c>
       <c r="AJ14" t="n">
-        <v>5198.755988455989</v>
+        <v>55.06464387464388</v>
       </c>
       <c r="AK14" t="n">
-        <v>-6.7</v>
+        <v>18.9</v>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>Aging</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Mature Accumulation</t>
+          <t>Confirmed Accumulation</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
@@ -3773,22 +3773,22 @@
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>04-08-2026</t>
+          <t>05-08-2026</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>31-08-2026</t>
+          <t>22-09-2026</t>
         </is>
       </c>
       <c r="AQ14" t="n">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="AR14" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AS14" t="n">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="AT14" t="n">
         <v>0</v>
@@ -3797,10 +3797,10 @@
         <v>0</v>
       </c>
       <c r="AV14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AW14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX14" t="n">
         <v>6</v>
@@ -3812,13 +3812,13 @@
         <v>0</v>
       </c>
       <c r="BA14" t="n">
-        <v>0</v>
+        <v>10009832</v>
       </c>
       <c r="BB14" t="n">
-        <v>19879002</v>
+        <v>10009832</v>
       </c>
       <c r="BC14" t="n">
-        <v>72054758</v>
+        <v>28991535</v>
       </c>
       <c r="BD14" t="n">
         <v>0</v>
@@ -3854,10 +3854,10 @@
         <v>0</v>
       </c>
       <c r="BO14" t="n">
-        <v>0</v>
+        <v>10009832</v>
       </c>
       <c r="BP14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BQ14" t="n">
         <v>0</v>
@@ -3941,10 +3941,10 @@
         </is>
       </c>
       <c r="V15" t="n">
-        <v>2.349</v>
+        <v>2.354</v>
       </c>
       <c r="W15" t="n">
-        <v>2499</v>
+        <v>2494</v>
       </c>
       <c r="X15" t="n">
         <v>196</v>
@@ -4173,13 +4173,13 @@
         </is>
       </c>
       <c r="V16" t="n">
-        <v>0.05</v>
+        <v>0.052</v>
       </c>
       <c r="W16" t="n">
-        <v>1643</v>
+        <v>1584</v>
       </c>
       <c r="X16" t="n">
-        <v>22.1</v>
+        <v>21.3</v>
       </c>
       <c r="Y16" t="n">
         <v>55</v>
@@ -4405,13 +4405,13 @@
         </is>
       </c>
       <c r="V17" t="n">
-        <v>1.472</v>
+        <v>1.513</v>
       </c>
       <c r="W17" t="n">
-        <v>9192</v>
+        <v>8944</v>
       </c>
       <c r="X17" t="n">
-        <v>1547</v>
+        <v>1506</v>
       </c>
       <c r="Y17" t="n">
         <v>-53</v>
@@ -4637,13 +4637,13 @@
         </is>
       </c>
       <c r="V18" t="n">
-        <v>0.125</v>
+        <v>0.129</v>
       </c>
       <c r="W18" t="n">
-        <v>2516</v>
+        <v>2434</v>
       </c>
       <c r="X18" t="n">
-        <v>22</v>
+        <v>21.3</v>
       </c>
       <c r="Y18" t="n">
         <v>-3</v>
@@ -4869,13 +4869,13 @@
         </is>
       </c>
       <c r="V19" t="n">
-        <v>0.065</v>
+        <v>0.063</v>
       </c>
       <c r="W19" t="n">
-        <v>874</v>
+        <v>891</v>
       </c>
       <c r="X19" t="n">
-        <v>22.1</v>
+        <v>22.5</v>
       </c>
       <c r="Y19" t="n">
         <v>19</v>
@@ -5099,13 +5099,13 @@
         </is>
       </c>
       <c r="V20" t="n">
-        <v>0.176</v>
+        <v>0.178</v>
       </c>
       <c r="W20" t="n">
-        <v>964</v>
+        <v>954</v>
       </c>
       <c r="X20" t="n">
-        <v>39.6</v>
+        <v>39.2</v>
       </c>
       <c r="Y20" t="n">
         <v>2</v>
@@ -5331,13 +5331,13 @@
         </is>
       </c>
       <c r="V21" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.57</v>
       </c>
       <c r="W21" t="n">
-        <v>2534</v>
+        <v>2507</v>
       </c>
       <c r="X21" t="n">
-        <v>20.8</v>
+        <v>20.6</v>
       </c>
       <c r="Y21" t="n">
         <v>8</v>
@@ -5563,13 +5563,13 @@
         </is>
       </c>
       <c r="V22" t="n">
-        <v>0.066</v>
+        <v>0.067</v>
       </c>
       <c r="W22" t="n">
-        <v>1672</v>
+        <v>1657</v>
       </c>
       <c r="X22" t="n">
-        <v>38.4</v>
+        <v>38</v>
       </c>
       <c r="Y22" t="n">
         <v>20</v>
@@ -5795,10 +5795,10 @@
         </is>
       </c>
       <c r="V23" t="n">
-        <v>1.742</v>
+        <v>1.77</v>
       </c>
       <c r="W23" t="n">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="X23" t="inlineStr"/>
       <c r="Y23" t="n">
@@ -6025,13 +6025,13 @@
         </is>
       </c>
       <c r="V24" t="n">
-        <v>3.144</v>
+        <v>3.205</v>
       </c>
       <c r="W24" t="n">
-        <v>626</v>
+        <v>614</v>
       </c>
       <c r="X24" t="n">
-        <v>18.9</v>
+        <v>18.6</v>
       </c>
       <c r="Y24" t="n">
         <v>30</v>
@@ -6254,10 +6254,10 @@
         <v>0.169</v>
       </c>
       <c r="W25" t="n">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="X25" t="n">
-        <v>54.6</v>
+        <v>54.7</v>
       </c>
       <c r="Y25" t="n">
         <v>3</v>
@@ -6483,13 +6483,13 @@
         </is>
       </c>
       <c r="V26" t="n">
-        <v>0.139</v>
+        <v>0.147</v>
       </c>
       <c r="W26" t="n">
-        <v>1524</v>
+        <v>1437</v>
       </c>
       <c r="X26" t="n">
-        <v>15.2</v>
+        <v>14.3</v>
       </c>
       <c r="Y26" t="n">
         <v>152</v>
@@ -6715,13 +6715,13 @@
         </is>
       </c>
       <c r="V27" t="n">
-        <v>0.059</v>
+        <v>0.056</v>
       </c>
       <c r="W27" t="n">
-        <v>2163</v>
+        <v>2263</v>
       </c>
       <c r="X27" t="n">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="Y27" t="n">
         <v>13</v>
@@ -6947,13 +6947,13 @@
         </is>
       </c>
       <c r="V28" t="n">
-        <v>0.064</v>
+        <v>0.062</v>
       </c>
       <c r="W28" t="n">
-        <v>1746</v>
+        <v>1795</v>
       </c>
       <c r="X28" t="n">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="Y28" t="n">
         <v>-48</v>
@@ -7179,13 +7179,13 @@
         </is>
       </c>
       <c r="V29" t="n">
-        <v>0.323</v>
+        <v>0.319</v>
       </c>
       <c r="W29" t="n">
-        <v>58868</v>
+        <v>59531</v>
       </c>
       <c r="X29" t="n">
-        <v>22</v>
+        <v>22.2</v>
       </c>
       <c r="Y29" t="n">
         <v>5</v>
@@ -7411,13 +7411,13 @@
         </is>
       </c>
       <c r="V30" t="n">
-        <v>0.539</v>
+        <v>0.551</v>
       </c>
       <c r="W30" t="n">
-        <v>917</v>
+        <v>898</v>
       </c>
       <c r="X30" t="n">
-        <v>16.2</v>
+        <v>15.9</v>
       </c>
       <c r="Y30" t="n">
         <v>13</v>
@@ -7646,10 +7646,10 @@
         <v>0.008999999999999999</v>
       </c>
       <c r="W31" t="n">
-        <v>55449</v>
+        <v>54890</v>
       </c>
       <c r="X31" t="n">
-        <v>47</v>
+        <v>46.5</v>
       </c>
       <c r="Y31" t="n">
         <v>5</v>
@@ -7875,13 +7875,13 @@
         </is>
       </c>
       <c r="V32" t="n">
-        <v>0.336</v>
+        <v>0.343</v>
       </c>
       <c r="W32" t="n">
-        <v>962</v>
+        <v>943</v>
       </c>
       <c r="X32" t="n">
-        <v>13.5</v>
+        <v>13.2</v>
       </c>
       <c r="Y32" t="n">
         <v>13</v>
@@ -8107,13 +8107,13 @@
         </is>
       </c>
       <c r="V33" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="W33" t="n">
-        <v>651</v>
+        <v>665</v>
       </c>
       <c r="X33" t="n">
-        <v>10.6</v>
+        <v>10.8</v>
       </c>
       <c r="Y33" t="n">
         <v>-5</v>
@@ -8339,13 +8339,13 @@
         </is>
       </c>
       <c r="V34" t="n">
-        <v>0.168</v>
+        <v>0.173</v>
       </c>
       <c r="W34" t="n">
-        <v>3813</v>
+        <v>3689</v>
       </c>
       <c r="X34" t="n">
-        <v>7.18</v>
+        <v>6.95</v>
       </c>
       <c r="Y34" t="n">
         <v>2</v>
@@ -8499,12 +8499,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>GANESHCP</t>
+          <t>HTEL</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>GANESH CONSUMER PRODUCTS LIMITED</t>
+          <t>Hy-Tech Engineers Limited</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -8516,10 +8516,10 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F35" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G35" t="n">
         <v>4</v>
@@ -8528,28 +8528,28 @@
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>163.82</v>
+        <v>92.93000000000001</v>
       </c>
       <c r="J35" t="n">
-        <v>166</v>
+        <v>68.68000000000001</v>
       </c>
       <c r="K35" t="n">
-        <v>-1.3</v>
+        <v>35.3</v>
       </c>
       <c r="L35" t="n">
-        <v>64.08</v>
+        <v>71.36</v>
       </c>
       <c r="M35" t="n">
-        <v>0.8</v>
+        <v>0.86</v>
       </c>
       <c r="N35" t="n">
-        <v>8001009</v>
+        <v>8585000</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>8001009</v>
+        <v>8585000</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -8563,64 +8563,58 @@
         <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>02-09-2026</t>
+          <t>29-09-2026</t>
         </is>
       </c>
       <c r="V35" t="n">
-        <v>0.121</v>
+        <v>0.101</v>
       </c>
       <c r="W35" t="n">
-        <v>662</v>
+        <v>851</v>
       </c>
       <c r="X35" t="n">
-        <v>14.6</v>
+        <v>37</v>
       </c>
       <c r="Y35" t="n">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="Z35" t="n">
-        <v>21</v>
+        <v>8.44</v>
       </c>
       <c r="AA35" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="AB35" t="n">
-        <v>3.1</v>
+        <v>0.55</v>
       </c>
       <c r="AC35" t="n">
-        <v>19.3</v>
+        <v>23.9</v>
       </c>
       <c r="AD35" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.25</v>
       </c>
       <c r="AE35" t="b">
         <v>1</v>
       </c>
       <c r="AF35" t="n">
-        <v>11</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>163.05</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>185.56</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>-14.4</v>
-      </c>
+        <v>19.61</v>
+      </c>
+      <c r="AG35" t="inlineStr"/>
+      <c r="AH35" t="inlineStr"/>
+      <c r="AI35" t="inlineStr"/>
       <c r="AJ35" t="n">
-        <v>165.9960373443983</v>
+        <v>68.68000000000001</v>
       </c>
       <c r="AK35" t="n">
-        <v>-1.3</v>
+        <v>35.3</v>
       </c>
       <c r="AL35" t="inlineStr">
         <is>
-          <t>Aging</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
@@ -8630,27 +8624,27 @@
       </c>
       <c r="AN35" t="inlineStr">
         <is>
-          <t>Mature — Wait for Pullback</t>
+          <t>Late — Poor Entry</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>25-08-2026</t>
+          <t>29-09-2026</t>
         </is>
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>02-09-2026</t>
+          <t>29-09-2026</t>
         </is>
       </c>
       <c r="AQ35" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AR35" t="n">
-        <v>51</v>
+        <v>16</v>
       </c>
       <c r="AS35" t="n">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="AT35" t="n">
         <v>0</v>
@@ -8659,13 +8653,13 @@
         <v>0</v>
       </c>
       <c r="AV35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AX35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AY35" t="n">
         <v>0</v>
@@ -8674,13 +8668,13 @@
         <v>0</v>
       </c>
       <c r="BA35" t="n">
-        <v>0</v>
+        <v>8585000</v>
       </c>
       <c r="BB35" t="n">
-        <v>8001009</v>
+        <v>8585000</v>
       </c>
       <c r="BC35" t="n">
-        <v>8001009</v>
+        <v>8585000</v>
       </c>
       <c r="BD35" t="n">
         <v>0</v>
@@ -8716,7 +8710,7 @@
         <v>0</v>
       </c>
       <c r="BO35" t="n">
-        <v>0</v>
+        <v>8585000</v>
       </c>
       <c r="BP35" t="n">
         <v>1</v>
@@ -8731,16 +8725,16 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SRGHFL</t>
+          <t>GANESHCP</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SRG HOUSING FINANCE LIMITED</t>
+          <t>GANESH CONSUMER PRODUCTS LIMITED</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -8748,40 +8742,40 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="F36" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>112.2</v>
+        <v>163.82</v>
       </c>
       <c r="J36" t="n">
-        <v>132.2</v>
+        <v>166</v>
       </c>
       <c r="K36" t="n">
-        <v>-15.1</v>
+        <v>-1.3</v>
       </c>
       <c r="L36" t="n">
-        <v>67.83</v>
+        <v>64.08</v>
       </c>
       <c r="M36" t="n">
-        <v>1.98</v>
+        <v>0.8</v>
       </c>
       <c r="N36" t="n">
-        <v>19830410</v>
+        <v>8001009</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>19830410</v>
+        <v>8001009</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -8795,159 +8789,163 @@
         <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>16-09-2026</t>
+          <t>02-09-2026</t>
         </is>
       </c>
       <c r="V36" t="n">
-        <v>1.127</v>
+        <v>0.121</v>
       </c>
       <c r="W36" t="n">
-        <v>176</v>
+        <v>660</v>
       </c>
       <c r="X36" t="n">
-        <v>5.16</v>
+        <v>14.5</v>
       </c>
       <c r="Y36" t="n">
-        <v>31</v>
-      </c>
-      <c r="Z36" t="inlineStr"/>
+        <v>-1</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>21</v>
+      </c>
       <c r="AA36" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="AB36" t="n">
-        <v>5.39</v>
+        <v>3.1</v>
       </c>
       <c r="AC36" t="n">
-        <v>11.8</v>
+        <v>19.3</v>
       </c>
       <c r="AD36" t="n">
-        <v>2.89</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AE36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF36" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>11</v>
+      </c>
       <c r="AG36" t="n">
-        <v>204.82</v>
+        <v>163.05</v>
       </c>
       <c r="AH36" t="n">
-        <v>261.31</v>
+        <v>185.56</v>
       </c>
       <c r="AI36" t="n">
-        <v>-59.5</v>
+        <v>-14.4</v>
       </c>
       <c r="AJ36" t="n">
-        <v>132.2027333333333</v>
+        <v>165.9960373443983</v>
       </c>
       <c r="AK36" t="n">
-        <v>-15.1</v>
+        <v>-1.3</v>
       </c>
       <c r="AL36" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Aging</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Mature Accumulation</t>
         </is>
       </c>
       <c r="AN36" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Mature — Wait for Pullback</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>15-09-2026</t>
+          <t>25-08-2026</t>
         </is>
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>16-09-2026</t>
+          <t>02-09-2026</t>
         </is>
       </c>
       <c r="AQ36" t="n">
+        <v>8</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>51</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>43</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB36" t="n">
+        <v>8001009</v>
+      </c>
+      <c r="BC36" t="n">
+        <v>8001009</v>
+      </c>
+      <c r="BD36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP36" t="n">
         <v>1</v>
-      </c>
-      <c r="AR36" t="n">
-        <v>30</v>
-      </c>
-      <c r="AS36" t="n">
-        <v>29</v>
-      </c>
-      <c r="AT36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV36" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW36" t="n">
-        <v>3</v>
-      </c>
-      <c r="AX36" t="n">
-        <v>3</v>
-      </c>
-      <c r="AY36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA36" t="n">
-        <v>10052740</v>
-      </c>
-      <c r="BB36" t="n">
-        <v>19830410</v>
-      </c>
-      <c r="BC36" t="n">
-        <v>19830410</v>
-      </c>
-      <c r="BD36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO36" t="n">
-        <v>10052740</v>
-      </c>
-      <c r="BP36" t="n">
-        <v>2</v>
       </c>
       <c r="BQ36" t="n">
         <v>0</v>
@@ -8959,16 +8957,16 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>HTEL</t>
+          <t>GREENPANEL</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Hy-Tech Engineers Limited</t>
+          <t>Greenpanel Industries Limited</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -8976,101 +8974,107 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="F37" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I37" t="n">
+        <v>147.83</v>
+      </c>
+      <c r="J37" t="n">
+        <v>155.33</v>
+      </c>
+      <c r="K37" t="n">
+        <v>-4.8</v>
+      </c>
+      <c r="L37" t="n">
+        <v>53.12</v>
+      </c>
+      <c r="M37" t="n">
+        <v>19.88</v>
+      </c>
+      <c r="N37" t="n">
+        <v>198797495</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
+        <v>198797495</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>Net Buying</t>
+        </is>
+      </c>
+      <c r="S37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
         <v>4</v>
       </c>
-      <c r="H37" t="n">
-        <v>0</v>
-      </c>
-      <c r="I37" t="n">
-        <v>92.93000000000001</v>
-      </c>
-      <c r="J37" t="n">
-        <v>68.68000000000001</v>
-      </c>
-      <c r="K37" t="n">
-        <v>35.3</v>
-      </c>
-      <c r="L37" t="n">
-        <v>71.36</v>
-      </c>
-      <c r="M37" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="N37" t="n">
-        <v>8585000</v>
-      </c>
-      <c r="O37" t="n">
-        <v>0</v>
-      </c>
-      <c r="P37" t="n">
-        <v>8585000</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>Net Buying</t>
-        </is>
-      </c>
-      <c r="S37" t="b">
-        <v>0</v>
-      </c>
-      <c r="T37" t="n">
-        <v>1</v>
-      </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>29-09-2026</t>
+          <t>18-09-2026</t>
         </is>
       </c>
       <c r="V37" t="n">
-        <v>0.097</v>
+        <v>1.136</v>
       </c>
       <c r="W37" t="n">
-        <v>881</v>
+        <v>1750</v>
       </c>
       <c r="X37" t="n">
-        <v>38.4</v>
+        <v>260</v>
       </c>
       <c r="Y37" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="Z37" t="n">
-        <v>8.44</v>
+        <v>29.89</v>
       </c>
       <c r="AA37" t="n">
-        <v>39</v>
+        <v>-69</v>
       </c>
       <c r="AB37" t="n">
-        <v>0.55</v>
+        <v>0.1</v>
       </c>
       <c r="AC37" t="n">
-        <v>23.9</v>
+        <v>-0.4</v>
       </c>
       <c r="AD37" t="n">
-        <v>0.25</v>
+        <v>0.27</v>
       </c>
       <c r="AE37" t="b">
         <v>1</v>
       </c>
       <c r="AF37" t="n">
-        <v>19.61</v>
-      </c>
-      <c r="AG37" t="inlineStr"/>
-      <c r="AH37" t="inlineStr"/>
-      <c r="AI37" t="inlineStr"/>
+        <v>8.539999999999999</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>164.4</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>194.94</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>-28.7</v>
+      </c>
       <c r="AJ37" t="n">
-        <v>68.68000000000001</v>
+        <v>155.3329934404582</v>
       </c>
       <c r="AK37" t="n">
-        <v>35.3</v>
+        <v>-4.8</v>
       </c>
       <c r="AL37" t="inlineStr">
         <is>
@@ -9079,32 +9083,32 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>Mature Accumulation</t>
+          <t>Confirmed Accumulation</t>
         </is>
       </c>
       <c r="AN37" t="inlineStr">
         <is>
-          <t>Late — Poor Entry</t>
+          <t>Confirmed Accumulation</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>29-09-2026</t>
+          <t>28-08-2026</t>
         </is>
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>29-09-2026</t>
+          <t>18-09-2026</t>
         </is>
       </c>
       <c r="AQ37" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AR37" t="n">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="AS37" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="AT37" t="n">
         <v>0</v>
@@ -9113,13 +9117,13 @@
         <v>0</v>
       </c>
       <c r="AV37" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AW37" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AX37" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AY37" t="n">
         <v>0</v>
@@ -9128,13 +9132,13 @@
         <v>0</v>
       </c>
       <c r="BA37" t="n">
-        <v>8585000</v>
+        <v>188893345</v>
       </c>
       <c r="BB37" t="n">
-        <v>8585000</v>
+        <v>198797495</v>
       </c>
       <c r="BC37" t="n">
-        <v>8585000</v>
+        <v>198797495</v>
       </c>
       <c r="BD37" t="n">
         <v>0</v>
@@ -9170,10 +9174,10 @@
         <v>0</v>
       </c>
       <c r="BO37" t="n">
-        <v>8585000</v>
+        <v>188893345</v>
       </c>
       <c r="BP37" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BQ37" t="n">
         <v>0</v>
@@ -9185,57 +9189,57 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>GREENPANEL</t>
+          <t>SRGHFL</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Greenpanel Industries Limited</t>
+          <t>SRG HOUSING FINANCE LIMITED</t>
         </is>
       </c>
       <c r="C38" t="n">
+        <v>17</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Avoid</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
         <v>15</v>
       </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Avoid</t>
-        </is>
-      </c>
-      <c r="E38" t="n">
-        <v>16</v>
-      </c>
       <c r="F38" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>147.83</v>
+        <v>112.2</v>
       </c>
       <c r="J38" t="n">
-        <v>155.33</v>
+        <v>132.2</v>
       </c>
       <c r="K38" t="n">
-        <v>-4.8</v>
+        <v>-15.1</v>
       </c>
       <c r="L38" t="n">
-        <v>53.12</v>
+        <v>67.83</v>
       </c>
       <c r="M38" t="n">
-        <v>19.88</v>
+        <v>1.98</v>
       </c>
       <c r="N38" t="n">
-        <v>198797495</v>
+        <v>19830410</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>198797495</v>
+        <v>19830410</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -9249,94 +9253,90 @@
         <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>18-09-2026</t>
+          <t>16-09-2026</t>
         </is>
       </c>
       <c r="V38" t="n">
-        <v>1.097</v>
+        <v>1.102</v>
       </c>
       <c r="W38" t="n">
-        <v>1813</v>
+        <v>180</v>
       </c>
       <c r="X38" t="n">
-        <v>270</v>
+        <v>5.27</v>
       </c>
       <c r="Y38" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>29.89</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="Z38" t="inlineStr"/>
       <c r="AA38" t="n">
-        <v>-69</v>
+        <v>35</v>
       </c>
       <c r="AB38" t="n">
-        <v>0.1</v>
+        <v>5.39</v>
       </c>
       <c r="AC38" t="n">
-        <v>-0.4</v>
+        <v>11.8</v>
       </c>
       <c r="AD38" t="n">
-        <v>0.27</v>
+        <v>2.89</v>
       </c>
       <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="n">
+        <v>204.82</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>261.31</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>-59.5</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>132.2027333333333</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>-15.1</v>
+      </c>
+      <c r="AL38" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>Confirmed Accumulation</t>
+        </is>
+      </c>
+      <c r="AN38" t="inlineStr">
+        <is>
+          <t>Confirmed Accumulation</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>15-09-2026</t>
+        </is>
+      </c>
+      <c r="AP38" t="inlineStr">
+        <is>
+          <t>16-09-2026</t>
+        </is>
+      </c>
+      <c r="AQ38" t="n">
         <v>1</v>
       </c>
-      <c r="AF38" t="n">
-        <v>8.539999999999999</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>164.4</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>194.94</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>-28.7</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>155.3329934404582</v>
-      </c>
-      <c r="AK38" t="n">
-        <v>-4.8</v>
-      </c>
-      <c r="AL38" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>Confirmed Accumulation</t>
-        </is>
-      </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>Confirmed Accumulation</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>28-08-2026</t>
-        </is>
-      </c>
-      <c r="AP38" t="inlineStr">
-        <is>
-          <t>18-09-2026</t>
-        </is>
-      </c>
-      <c r="AQ38" t="n">
-        <v>21</v>
-      </c>
       <c r="AR38" t="n">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="AS38" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AT38" t="n">
         <v>0</v>
@@ -9345,13 +9345,13 @@
         <v>0</v>
       </c>
       <c r="AV38" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW38" t="n">
         <v>3</v>
       </c>
-      <c r="AW38" t="n">
-        <v>4</v>
-      </c>
       <c r="AX38" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AY38" t="n">
         <v>0</v>
@@ -9360,13 +9360,13 @@
         <v>0</v>
       </c>
       <c r="BA38" t="n">
-        <v>188893345</v>
+        <v>10052740</v>
       </c>
       <c r="BB38" t="n">
-        <v>198797495</v>
+        <v>19830410</v>
       </c>
       <c r="BC38" t="n">
-        <v>198797495</v>
+        <v>19830410</v>
       </c>
       <c r="BD38" t="n">
         <v>0</v>
@@ -9402,10 +9402,10 @@
         <v>0</v>
       </c>
       <c r="BO38" t="n">
-        <v>188893345</v>
+        <v>10052740</v>
       </c>
       <c r="BP38" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BQ38" t="n">
         <v>0</v>
@@ -9492,10 +9492,10 @@
         <v>0.01</v>
       </c>
       <c r="W39" t="n">
-        <v>14982</v>
+        <v>15318</v>
       </c>
       <c r="X39" t="n">
-        <v>13.8</v>
+        <v>14.1</v>
       </c>
       <c r="Y39" t="n">
         <v>28</v>
@@ -9723,7 +9723,7 @@
       <c r="V40" t="inlineStr"/>
       <c r="W40" t="inlineStr"/>
       <c r="X40" t="n">
-        <v>5.68</v>
+        <v>5.64</v>
       </c>
       <c r="Y40" t="n">
         <v>-68</v>
@@ -10184,10 +10184,10 @@
         <v>0.004</v>
       </c>
       <c r="W42" t="n">
-        <v>47532</v>
+        <v>45263</v>
       </c>
       <c r="X42" t="n">
-        <v>352</v>
+        <v>335</v>
       </c>
       <c r="Y42" t="n">
         <v>26</v>
@@ -10413,13 +10413,13 @@
         </is>
       </c>
       <c r="V43" t="n">
-        <v>0.368</v>
+        <v>0.374</v>
       </c>
       <c r="W43" t="n">
-        <v>1068</v>
+        <v>1052</v>
       </c>
       <c r="X43" t="n">
-        <v>54.4</v>
+        <v>53.6</v>
       </c>
       <c r="Y43" t="n">
         <v>21</v>
@@ -10437,7 +10437,7 @@
         <v>1.58</v>
       </c>
       <c r="AD43" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
@@ -10645,13 +10645,13 @@
         </is>
       </c>
       <c r="V44" t="n">
-        <v>1.662</v>
+        <v>1.633</v>
       </c>
       <c r="W44" t="n">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="X44" t="n">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="Y44" t="n">
         <v>-14</v>
@@ -10880,7 +10880,7 @@
         <v>0.263</v>
       </c>
       <c r="W45" t="n">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="X45" t="n">
         <v>26.9</v>
@@ -11109,10 +11109,10 @@
         </is>
       </c>
       <c r="V46" t="n">
-        <v>4.473</v>
+        <v>4.545</v>
       </c>
       <c r="W46" t="n">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="X46" t="inlineStr"/>
       <c r="Y46" t="n">
@@ -11339,13 +11339,13 @@
         </is>
       </c>
       <c r="V47" t="n">
-        <v>0.525</v>
+        <v>0.523</v>
       </c>
       <c r="W47" t="n">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="X47" t="n">
-        <v>35.3</v>
+        <v>35.4</v>
       </c>
       <c r="Y47" t="n">
         <v>21</v>
@@ -11574,10 +11574,10 @@
         <v>0.043</v>
       </c>
       <c r="W48" t="n">
-        <v>1620</v>
+        <v>1610</v>
       </c>
       <c r="X48" t="n">
-        <v>21.2</v>
+        <v>21</v>
       </c>
       <c r="Y48" t="n">
         <v>10</v>
@@ -11803,13 +11803,13 @@
         </is>
       </c>
       <c r="V49" t="n">
-        <v>0.504</v>
+        <v>0.512</v>
       </c>
       <c r="W49" t="n">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="X49" t="n">
-        <v>36.9</v>
+        <v>36.5</v>
       </c>
       <c r="Y49" t="n">
         <v>-44</v>
@@ -12035,13 +12035,13 @@
         </is>
       </c>
       <c r="V50" t="n">
-        <v>0.829</v>
+        <v>0.827</v>
       </c>
       <c r="W50" t="n">
-        <v>3811</v>
+        <v>3821</v>
       </c>
       <c r="X50" t="n">
-        <v>26.7</v>
+        <v>26.8</v>
       </c>
       <c r="Y50" t="n">
         <v>2</v>
@@ -12267,13 +12267,13 @@
         </is>
       </c>
       <c r="V51" t="n">
-        <v>0.673</v>
+        <v>0.677</v>
       </c>
       <c r="W51" t="n">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="X51" t="n">
-        <v>1126</v>
+        <v>1121</v>
       </c>
       <c r="Y51" t="n">
         <v>-61</v>
@@ -12495,13 +12495,13 @@
         </is>
       </c>
       <c r="V52" t="n">
-        <v>0.044</v>
+        <v>0.045</v>
       </c>
       <c r="W52" t="n">
-        <v>5239</v>
+        <v>5185</v>
       </c>
       <c r="X52" t="n">
-        <v>27.2</v>
+        <v>27</v>
       </c>
       <c r="Y52" t="n">
         <v>13</v>
@@ -12727,10 +12727,10 @@
         </is>
       </c>
       <c r="V53" t="n">
-        <v>0.236</v>
+        <v>0.235</v>
       </c>
       <c r="W53" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="X53" t="n">
         <v>14.5</v>
@@ -12959,13 +12959,13 @@
         </is>
       </c>
       <c r="V54" t="n">
-        <v>0.23</v>
+        <v>0.232</v>
       </c>
       <c r="W54" t="n">
-        <v>1734</v>
+        <v>1721</v>
       </c>
       <c r="X54" t="n">
-        <v>18.4</v>
+        <v>18.2</v>
       </c>
       <c r="Y54" t="n">
         <v>-3</v>
@@ -13191,13 +13191,13 @@
         </is>
       </c>
       <c r="V55" t="n">
-        <v>0.366</v>
+        <v>0.36</v>
       </c>
       <c r="W55" t="n">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="X55" t="n">
-        <v>94.8</v>
+        <v>96.3</v>
       </c>
       <c r="Y55" t="n">
         <v>246</v>
@@ -13577,154 +13577,158 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>PAISALO</t>
+          <t>FOCUS</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>PAISALO DIGITAL LIMITED</t>
+          <t>Focus Lighting And Fixtures Limited</t>
         </is>
       </c>
       <c r="C57" t="n">
+        <v>2</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Avoid</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>7</v>
+      </c>
+      <c r="F57" t="n">
+        <v>4</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I57" t="n">
+        <v>58.37</v>
+      </c>
+      <c r="J57" t="n">
+        <v>64.68000000000001</v>
+      </c>
+      <c r="K57" t="n">
+        <v>-9.800000000000001</v>
+      </c>
+      <c r="L57" t="n">
+        <v>56.09</v>
+      </c>
+      <c r="M57" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="N57" t="n">
+        <v>11750494</v>
+      </c>
+      <c r="O57" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" t="n">
+        <v>11750494</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>Net Buying</t>
+        </is>
+      </c>
+      <c r="S57" t="b">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>4</v>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>11-09-2026</t>
+        </is>
+      </c>
+      <c r="V57" t="n">
+        <v>0.314</v>
+      </c>
+      <c r="W57" t="n">
+        <v>374</v>
+      </c>
+      <c r="X57" t="n">
+        <v>61.1</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>-54</v>
+      </c>
+      <c r="AB57" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="AE57" t="b">
         <v>1</v>
       </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>Avoid</t>
-        </is>
-      </c>
-      <c r="E57" t="n">
-        <v>-2</v>
-      </c>
-      <c r="F57" t="n">
-        <v>7</v>
-      </c>
-      <c r="G57" t="n">
-        <v>17</v>
-      </c>
-      <c r="H57" t="n">
-        <v>-16</v>
-      </c>
-      <c r="I57" t="n">
-        <v>81.70999999999999</v>
-      </c>
-      <c r="J57" t="n">
-        <v>93.86</v>
-      </c>
-      <c r="K57" t="n">
-        <v>-12.9</v>
-      </c>
-      <c r="L57" t="n">
-        <v>50.38</v>
-      </c>
-      <c r="M57" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="N57" t="n">
-        <v>21588176</v>
-      </c>
-      <c r="O57" t="n">
-        <v>0</v>
-      </c>
-      <c r="P57" t="n">
-        <v>21588176</v>
-      </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
-      <c r="R57" t="inlineStr">
-        <is>
-          <t>Net Buying</t>
-        </is>
-      </c>
-      <c r="S57" t="b">
-        <v>0</v>
-      </c>
-      <c r="T57" t="n">
-        <v>2</v>
-      </c>
-      <c r="U57" t="inlineStr">
-        <is>
-          <t>22-09-2026</t>
-        </is>
-      </c>
-      <c r="V57" t="n">
-        <v>0.029</v>
-      </c>
-      <c r="W57" t="n">
-        <v>7470</v>
-      </c>
-      <c r="X57" t="n">
-        <v>29.9</v>
-      </c>
-      <c r="Y57" t="n">
-        <v>25</v>
-      </c>
-      <c r="Z57" t="inlineStr"/>
-      <c r="AA57" t="n">
-        <v>23</v>
-      </c>
-      <c r="AB57" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="AC57" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="AD57" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="AE57" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF57" t="inlineStr"/>
+      <c r="AF57" t="n">
+        <v>13.36</v>
+      </c>
       <c r="AG57" t="n">
-        <v>76.69</v>
+        <v>62.59</v>
       </c>
       <c r="AH57" t="n">
-        <v>54.08</v>
+        <v>72.51000000000001</v>
       </c>
       <c r="AI57" t="n">
-        <v>107.2</v>
+        <v>-13.3</v>
       </c>
       <c r="AJ57" t="n">
-        <v>93.86000243474027</v>
+        <v>64.68221176341068</v>
       </c>
       <c r="AK57" t="n">
-        <v>-12.9</v>
+        <v>-9.800000000000001</v>
       </c>
       <c r="AL57" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Aging</t>
         </is>
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Mature Accumulation</t>
         </is>
       </c>
       <c r="AN57" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Mature — Wait for Pullback</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>22-09-2026</t>
+          <t>27-08-2026</t>
         </is>
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>22-09-2026</t>
+          <t>11-09-2026</t>
         </is>
       </c>
       <c r="AQ57" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AR57" t="n">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="AS57" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="AT57" t="n">
         <v>0</v>
@@ -13733,13 +13737,13 @@
         <v>0</v>
       </c>
       <c r="AV57" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW57" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AX57" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AY57" t="n">
         <v>0</v>
@@ -13748,13 +13752,13 @@
         <v>0</v>
       </c>
       <c r="BA57" t="n">
-        <v>21588176</v>
+        <v>0</v>
       </c>
       <c r="BB57" t="n">
-        <v>21588176</v>
+        <v>11750494</v>
       </c>
       <c r="BC57" t="n">
-        <v>21588176</v>
+        <v>11750494</v>
       </c>
       <c r="BD57" t="n">
         <v>0</v>
@@ -13790,10 +13794,10 @@
         <v>0</v>
       </c>
       <c r="BO57" t="n">
-        <v>21588176</v>
+        <v>0</v>
       </c>
       <c r="BP57" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BQ57" t="n">
         <v>0</v>
@@ -13805,16 +13809,16 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>RAMASTEEL</t>
+          <t>PAISALO</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Rama Steel Tubes Limited</t>
+          <t>PAISALO DIGITAL LIMITED</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -13822,47 +13826,47 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>3</v>
+        <v>-2</v>
       </c>
       <c r="F58" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G58" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="H58" t="n">
-        <v>-14</v>
+        <v>-16</v>
       </c>
       <c r="I58" t="n">
-        <v>4.01</v>
+        <v>81.70999999999999</v>
       </c>
       <c r="J58" t="n">
-        <v>4.45</v>
+        <v>93.86</v>
       </c>
       <c r="K58" t="n">
-        <v>-9.9</v>
+        <v>-12.9</v>
       </c>
       <c r="L58" t="n">
-        <v>57.22</v>
+        <v>50.38</v>
       </c>
       <c r="M58" t="n">
-        <v>3.87</v>
+        <v>2.16</v>
       </c>
       <c r="N58" t="n">
-        <v>38720906</v>
+        <v>21588176</v>
       </c>
       <c r="O58" t="n">
-        <v>22662309</v>
+        <v>0</v>
       </c>
       <c r="P58" t="n">
-        <v>16058597</v>
+        <v>21588176</v>
       </c>
       <c r="Q58" t="n">
-        <v>58.53</v>
+        <v>0</v>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>Net Buying with Selling</t>
+          <t>Net Buying</t>
         </is>
       </c>
       <c r="S58" t="b">
@@ -13873,56 +13877,52 @@
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>22-09-2026</t>
         </is>
       </c>
       <c r="V58" t="n">
-        <v>0.245</v>
+        <v>0.029</v>
       </c>
       <c r="W58" t="n">
-        <v>656</v>
+        <v>7449</v>
       </c>
       <c r="X58" t="n">
-        <v>53.4</v>
+        <v>29.8</v>
       </c>
       <c r="Y58" t="n">
-        <v>-4</v>
-      </c>
-      <c r="Z58" t="n">
-        <v>3.7</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="Z58" t="inlineStr"/>
       <c r="AA58" t="n">
-        <v>-31</v>
+        <v>23</v>
       </c>
       <c r="AB58" t="n">
-        <v>0.03</v>
+        <v>0.67</v>
       </c>
       <c r="AC58" t="n">
-        <v>6.01</v>
+        <v>12.4</v>
       </c>
       <c r="AD58" t="n">
-        <v>0.14</v>
+        <v>2.41</v>
       </c>
       <c r="AE58" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF58" t="n">
-        <v>2.13</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="n">
-        <v>4.29</v>
+        <v>76.69</v>
       </c>
       <c r="AH58" t="n">
-        <v>5.65</v>
+        <v>54.08</v>
       </c>
       <c r="AI58" t="n">
-        <v>-21.8</v>
+        <v>107.2</v>
       </c>
       <c r="AJ58" t="n">
-        <v>4.450289578118512</v>
+        <v>93.86000243474027</v>
       </c>
       <c r="AK58" t="n">
-        <v>-9.9</v>
+        <v>-12.9</v>
       </c>
       <c r="AL58" t="inlineStr">
         <is>
@@ -13941,22 +13941,22 @@
       </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>22-09-2026</t>
         </is>
       </c>
       <c r="AP58" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>22-09-2026</t>
         </is>
       </c>
       <c r="AQ58" t="n">
         <v>0</v>
       </c>
       <c r="AR58" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="AS58" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="AT58" t="n">
         <v>0</v>
@@ -13980,13 +13980,13 @@
         <v>0</v>
       </c>
       <c r="BA58" t="n">
-        <v>38720906</v>
+        <v>21588176</v>
       </c>
       <c r="BB58" t="n">
-        <v>38720906</v>
+        <v>21588176</v>
       </c>
       <c r="BC58" t="n">
-        <v>38720906</v>
+        <v>21588176</v>
       </c>
       <c r="BD58" t="n">
         <v>0</v>
@@ -13998,10 +13998,10 @@
         <v>0</v>
       </c>
       <c r="BG58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BH58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI58" t="n">
         <v>0</v>
@@ -14013,22 +14013,22 @@
         <v>0</v>
       </c>
       <c r="BL58" t="n">
-        <v>22662309</v>
+        <v>0</v>
       </c>
       <c r="BM58" t="n">
-        <v>22662309</v>
+        <v>0</v>
       </c>
       <c r="BN58" t="n">
         <v>0</v>
       </c>
       <c r="BO58" t="n">
-        <v>38720906</v>
+        <v>21588176</v>
       </c>
       <c r="BP58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BQ58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BR58" t="n">
         <v>0</v>
@@ -14037,12 +14037,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>LINC</t>
+          <t>RAMASTEEL</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>LINC LIMITED</t>
+          <t>Rama Steel Tubes Limited</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -14054,43 +14054,43 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F59" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="I59" t="n">
-        <v>85.16</v>
+        <v>4.01</v>
       </c>
       <c r="J59" t="n">
-        <v>91.15000000000001</v>
+        <v>4.45</v>
       </c>
       <c r="K59" t="n">
-        <v>-6.6</v>
+        <v>-9.9</v>
       </c>
       <c r="L59" t="n">
-        <v>59.44</v>
+        <v>57.22</v>
       </c>
       <c r="M59" t="n">
-        <v>2.28</v>
+        <v>3.87</v>
       </c>
       <c r="N59" t="n">
-        <v>22833998</v>
+        <v>38720906</v>
       </c>
       <c r="O59" t="n">
-        <v>12934559</v>
+        <v>22662309</v>
       </c>
       <c r="P59" t="n">
-        <v>9899439</v>
+        <v>16058597</v>
       </c>
       <c r="Q59" t="n">
-        <v>56.65</v>
+        <v>58.53</v>
       </c>
       <c r="R59" t="inlineStr">
         <is>
@@ -14101,60 +14101,60 @@
         <v>0</v>
       </c>
       <c r="T59" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>29-09-2026</t>
+          <t>30-09-2026</t>
         </is>
       </c>
       <c r="V59" t="n">
-        <v>0.195</v>
+        <v>0.246</v>
       </c>
       <c r="W59" t="n">
-        <v>507</v>
+        <v>653</v>
       </c>
       <c r="X59" t="n">
-        <v>14.7</v>
+        <v>53.1</v>
       </c>
       <c r="Y59" t="n">
-        <v>-1</v>
+        <v>-4</v>
       </c>
       <c r="Z59" t="n">
-        <v>10.45</v>
+        <v>3.7</v>
       </c>
       <c r="AA59" t="n">
-        <v>-9</v>
+        <v>-31</v>
       </c>
       <c r="AB59" t="n">
-        <v>0.86</v>
+        <v>0.03</v>
       </c>
       <c r="AC59" t="n">
-        <v>19.1</v>
+        <v>6.01</v>
       </c>
       <c r="AD59" t="n">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
       <c r="AE59" t="b">
         <v>1</v>
       </c>
       <c r="AF59" t="n">
-        <v>7.7</v>
+        <v>2.13</v>
       </c>
       <c r="AG59" t="n">
-        <v>93.65000000000001</v>
+        <v>4.29</v>
       </c>
       <c r="AH59" t="n">
-        <v>102.27</v>
+        <v>5.65</v>
       </c>
       <c r="AI59" t="n">
-        <v>-13.6</v>
+        <v>-21.8</v>
       </c>
       <c r="AJ59" t="n">
-        <v>91.15368463073852</v>
+        <v>4.450289578118512</v>
       </c>
       <c r="AK59" t="n">
-        <v>-6.6</v>
+        <v>-9.9</v>
       </c>
       <c r="AL59" t="inlineStr">
         <is>
@@ -14173,22 +14173,22 @@
       </c>
       <c r="AO59" t="inlineStr">
         <is>
-          <t>21-09-2026</t>
+          <t>30-09-2026</t>
         </is>
       </c>
       <c r="AP59" t="inlineStr">
         <is>
-          <t>29-09-2026</t>
+          <t>30-09-2026</t>
         </is>
       </c>
       <c r="AQ59" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AR59" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="AS59" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AT59" t="n">
         <v>0</v>
@@ -14197,13 +14197,13 @@
         <v>0</v>
       </c>
       <c r="AV59" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AW59" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AX59" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AY59" t="n">
         <v>0</v>
@@ -14212,13 +14212,13 @@
         <v>0</v>
       </c>
       <c r="BA59" t="n">
-        <v>22833998</v>
+        <v>38720906</v>
       </c>
       <c r="BB59" t="n">
-        <v>22833998</v>
+        <v>38720906</v>
       </c>
       <c r="BC59" t="n">
-        <v>22833998</v>
+        <v>38720906</v>
       </c>
       <c r="BD59" t="n">
         <v>0</v>
@@ -14227,7 +14227,7 @@
         <v>0</v>
       </c>
       <c r="BF59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BG59" t="n">
         <v>1</v>
@@ -14242,22 +14242,22 @@
         <v>0</v>
       </c>
       <c r="BK59" t="n">
-        <v>12934559</v>
+        <v>0</v>
       </c>
       <c r="BL59" t="n">
-        <v>12934559</v>
+        <v>22662309</v>
       </c>
       <c r="BM59" t="n">
-        <v>12934559</v>
+        <v>22662309</v>
       </c>
       <c r="BN59" t="n">
         <v>0</v>
       </c>
       <c r="BO59" t="n">
-        <v>9899439</v>
+        <v>38720906</v>
       </c>
       <c r="BP59" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BQ59" t="n">
         <v>1</v>
@@ -14269,12 +14269,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>LIBERTSHOE</t>
+          <t>LINC</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>LIBERTY SHOES LIMITED</t>
+          <t>LINC LIMITED</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -14286,47 +14286,47 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F60" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>0</v>
+        <v>-13</v>
       </c>
       <c r="I60" t="n">
-        <v>209.08</v>
+        <v>85.16</v>
       </c>
       <c r="J60" t="n">
-        <v>244.24</v>
+        <v>91.15000000000001</v>
       </c>
       <c r="K60" t="n">
-        <v>-14.4</v>
+        <v>-6.6</v>
       </c>
       <c r="L60" t="n">
-        <v>58.5</v>
+        <v>59.44</v>
       </c>
       <c r="M60" t="n">
-        <v>1.71</v>
+        <v>2.28</v>
       </c>
       <c r="N60" t="n">
-        <v>17097005</v>
+        <v>22833998</v>
       </c>
       <c r="O60" t="n">
-        <v>0</v>
+        <v>12934559</v>
       </c>
       <c r="P60" t="n">
-        <v>17097005</v>
+        <v>9899439</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>56.65</v>
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>Net Buying</t>
+          <t>Net Buying with Selling</t>
         </is>
       </c>
       <c r="S60" t="b">
@@ -14337,90 +14337,90 @@
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>19-08-2026</t>
+          <t>29-09-2026</t>
         </is>
       </c>
       <c r="V60" t="n">
-        <v>0.48</v>
+        <v>0.181</v>
       </c>
       <c r="W60" t="n">
-        <v>356</v>
+        <v>547</v>
       </c>
       <c r="X60" t="n">
-        <v>41.8</v>
+        <v>15.9</v>
       </c>
       <c r="Y60" t="n">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="Z60" t="n">
-        <v>13.51</v>
+        <v>10.45</v>
       </c>
       <c r="AA60" t="n">
-        <v>-39</v>
+        <v>-9</v>
       </c>
       <c r="AB60" t="n">
-        <v>0.4</v>
+        <v>0.86</v>
       </c>
       <c r="AC60" t="n">
-        <v>7.91</v>
+        <v>19.1</v>
       </c>
       <c r="AD60" t="n">
-        <v>0.71</v>
+        <v>0.08</v>
       </c>
       <c r="AE60" t="b">
         <v>1</v>
       </c>
       <c r="AF60" t="n">
-        <v>7.95</v>
+        <v>7.7</v>
       </c>
       <c r="AG60" t="n">
-        <v>233.29</v>
+        <v>93.65000000000001</v>
       </c>
       <c r="AH60" t="n">
-        <v>248.92</v>
+        <v>102.27</v>
       </c>
       <c r="AI60" t="n">
-        <v>-19.3</v>
+        <v>-13.6</v>
       </c>
       <c r="AJ60" t="n">
-        <v>244.2429285714286</v>
+        <v>91.15368463073852</v>
       </c>
       <c r="AK60" t="n">
-        <v>-14.4</v>
+        <v>-6.6</v>
       </c>
       <c r="AL60" t="inlineStr">
         <is>
-          <t>Aging</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="AM60" t="inlineStr">
         <is>
-          <t>Mature Accumulation</t>
+          <t>Confirmed Accumulation</t>
         </is>
       </c>
       <c r="AN60" t="inlineStr">
         <is>
-          <t>Mature — Wait for Pullback</t>
+          <t>Confirmed Accumulation</t>
         </is>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
-          <t>17-08-2026</t>
+          <t>21-09-2026</t>
         </is>
       </c>
       <c r="AP60" t="inlineStr">
         <is>
-          <t>19-08-2026</t>
+          <t>29-09-2026</t>
         </is>
       </c>
       <c r="AQ60" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AR60" t="n">
-        <v>59</v>
+        <v>24</v>
       </c>
       <c r="AS60" t="n">
-        <v>57</v>
+        <v>16</v>
       </c>
       <c r="AT60" t="n">
         <v>0</v>
@@ -14429,7 +14429,7 @@
         <v>0</v>
       </c>
       <c r="AV60" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AW60" t="n">
         <v>5</v>
@@ -14444,13 +14444,13 @@
         <v>0</v>
       </c>
       <c r="BA60" t="n">
-        <v>0</v>
+        <v>22833998</v>
       </c>
       <c r="BB60" t="n">
-        <v>17097005</v>
+        <v>22833998</v>
       </c>
       <c r="BC60" t="n">
-        <v>17097005</v>
+        <v>22833998</v>
       </c>
       <c r="BD60" t="n">
         <v>0</v>
@@ -14459,13 +14459,13 @@
         <v>0</v>
       </c>
       <c r="BF60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BG60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BH60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BI60" t="n">
         <v>0</v>
@@ -14474,25 +14474,25 @@
         <v>0</v>
       </c>
       <c r="BK60" t="n">
-        <v>0</v>
+        <v>12934559</v>
       </c>
       <c r="BL60" t="n">
-        <v>0</v>
+        <v>12934559</v>
       </c>
       <c r="BM60" t="n">
-        <v>0</v>
+        <v>12934559</v>
       </c>
       <c r="BN60" t="n">
         <v>0</v>
       </c>
       <c r="BO60" t="n">
-        <v>0</v>
+        <v>9899439</v>
       </c>
       <c r="BP60" t="n">
+        <v>4</v>
+      </c>
+      <c r="BQ60" t="n">
         <v>1</v>
-      </c>
-      <c r="BQ60" t="n">
-        <v>0</v>
       </c>
       <c r="BR60" t="n">
         <v>0</v>
@@ -14501,12 +14501,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>WSI</t>
+          <t>LIBERTSHOE</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>W S Industries (I) Limited</t>
+          <t>LIBERTY SHOES LIMITED</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -14518,141 +14518,141 @@
         </is>
       </c>
       <c r="E61" t="n">
+        <v>7</v>
+      </c>
+      <c r="F61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" t="n">
+        <v>209.08</v>
+      </c>
+      <c r="J61" t="n">
+        <v>244.24</v>
+      </c>
+      <c r="K61" t="n">
+        <v>-14.4</v>
+      </c>
+      <c r="L61" t="n">
+        <v>58.5</v>
+      </c>
+      <c r="M61" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="N61" t="n">
+        <v>17097005</v>
+      </c>
+      <c r="O61" t="n">
+        <v>0</v>
+      </c>
+      <c r="P61" t="n">
+        <v>17097005</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>0</v>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>Net Buying</t>
+        </is>
+      </c>
+      <c r="S61" t="b">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>5</v>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>19-08-2026</t>
+        </is>
+      </c>
+      <c r="V61" t="n">
+        <v>0.478</v>
+      </c>
+      <c r="W61" t="n">
+        <v>358</v>
+      </c>
+      <c r="X61" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="Y61" t="n">
         <v>6</v>
       </c>
-      <c r="F61" t="n">
-        <v>-2</v>
-      </c>
-      <c r="G61" t="n">
-        <v>12</v>
-      </c>
-      <c r="H61" t="n">
-        <v>-18</v>
-      </c>
-      <c r="I61" t="n">
-        <v>63.86</v>
-      </c>
-      <c r="J61" t="n">
-        <v>59.88</v>
-      </c>
-      <c r="K61" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="L61" t="n">
-        <v>57.6</v>
-      </c>
-      <c r="M61" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="N61" t="n">
-        <v>14302785</v>
-      </c>
-      <c r="O61" t="n">
-        <v>0</v>
-      </c>
-      <c r="P61" t="n">
-        <v>14302785</v>
-      </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
-      <c r="R61" t="inlineStr">
-        <is>
-          <t>Net Buying</t>
-        </is>
-      </c>
-      <c r="S61" t="b">
-        <v>0</v>
-      </c>
-      <c r="T61" t="n">
-        <v>29</v>
-      </c>
-      <c r="U61" t="inlineStr">
-        <is>
-          <t>30-09-2026</t>
-        </is>
-      </c>
-      <c r="V61" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="W61" t="n">
-        <v>485</v>
-      </c>
-      <c r="X61" t="n">
-        <v>218</v>
-      </c>
-      <c r="Y61" t="n">
-        <v>-66</v>
-      </c>
       <c r="Z61" t="n">
-        <v>-2.47</v>
+        <v>13.51</v>
       </c>
       <c r="AA61" t="n">
-        <v>111</v>
+        <v>-39</v>
       </c>
       <c r="AB61" t="n">
-        <v>0.23</v>
+        <v>0.4</v>
       </c>
       <c r="AC61" t="n">
-        <v>2.04</v>
+        <v>7.91</v>
       </c>
       <c r="AD61" t="n">
-        <v>0.11</v>
+        <v>0.71</v>
       </c>
       <c r="AE61" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF61" t="n">
-        <v>-574.42</v>
+        <v>7.95</v>
       </c>
       <c r="AG61" t="n">
-        <v>58.61</v>
+        <v>233.29</v>
       </c>
       <c r="AH61" t="n">
-        <v>68.90000000000001</v>
+        <v>248.92</v>
       </c>
       <c r="AI61" t="n">
+        <v>-19.3</v>
+      </c>
+      <c r="AJ61" t="n">
+        <v>244.2429285714286</v>
+      </c>
+      <c r="AK61" t="n">
         <v>-14.4</v>
       </c>
-      <c r="AJ61" t="n">
-        <v>59.88437866354045</v>
-      </c>
-      <c r="AK61" t="n">
-        <v>6.6</v>
-      </c>
       <c r="AL61" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Aging</t>
         </is>
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Mature Accumulation</t>
         </is>
       </c>
       <c r="AN61" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Mature — Wait for Pullback</t>
         </is>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>14-08-2026</t>
+          <t>17-08-2026</t>
         </is>
       </c>
       <c r="AP61" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>19-08-2026</t>
         </is>
       </c>
       <c r="AQ61" t="n">
-        <v>47</v>
+        <v>2</v>
       </c>
       <c r="AR61" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="AS61" t="n">
-        <v>15</v>
+        <v>57</v>
       </c>
       <c r="AT61" t="n">
         <v>0</v>
@@ -14661,13 +14661,13 @@
         <v>0</v>
       </c>
       <c r="AV61" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AW61" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="AX61" t="n">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="AY61" t="n">
         <v>0</v>
@@ -14676,13 +14676,13 @@
         <v>0</v>
       </c>
       <c r="BA61" t="n">
-        <v>2503510</v>
+        <v>0</v>
       </c>
       <c r="BB61" t="n">
-        <v>13399767</v>
+        <v>17097005</v>
       </c>
       <c r="BC61" t="n">
-        <v>14302785</v>
+        <v>17097005</v>
       </c>
       <c r="BD61" t="n">
         <v>0</v>
@@ -14718,10 +14718,10 @@
         <v>0</v>
       </c>
       <c r="BO61" t="n">
-        <v>2503510</v>
+        <v>0</v>
       </c>
       <c r="BP61" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="BQ61" t="n">
         <v>0</v>
@@ -14733,12 +14733,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>EIEL</t>
+          <t>WSI</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>ENVIRO INFRA ENGINEERS LIMITED</t>
+          <t>W S Industries (I) Limited</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -14750,156 +14750,156 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F62" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="G62" t="n">
+        <v>12</v>
+      </c>
+      <c r="H62" t="n">
+        <v>-18</v>
+      </c>
+      <c r="I62" t="n">
+        <v>63.86</v>
+      </c>
+      <c r="J62" t="n">
+        <v>59.88</v>
+      </c>
+      <c r="K62" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="L62" t="n">
+        <v>57.6</v>
+      </c>
+      <c r="M62" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N62" t="n">
+        <v>14302785</v>
+      </c>
+      <c r="O62" t="n">
+        <v>0</v>
+      </c>
+      <c r="P62" t="n">
+        <v>14302785</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>0</v>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>Net Buying</t>
+        </is>
+      </c>
+      <c r="S62" t="b">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>29</v>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>30-09-2026</t>
+        </is>
+      </c>
+      <c r="V62" t="n">
+        <v>0.265</v>
+      </c>
+      <c r="W62" t="n">
+        <v>539</v>
+      </c>
+      <c r="X62" t="n">
+        <v>243</v>
+      </c>
+      <c r="Y62" t="n">
+        <v>-66</v>
+      </c>
+      <c r="Z62" t="n">
+        <v>-2.47</v>
+      </c>
+      <c r="AA62" t="n">
+        <v>111</v>
+      </c>
+      <c r="AB62" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="AC62" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AD62" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF62" t="n">
+        <v>-574.42</v>
+      </c>
+      <c r="AG62" t="n">
+        <v>58.61</v>
+      </c>
+      <c r="AH62" t="n">
+        <v>68.90000000000001</v>
+      </c>
+      <c r="AI62" t="n">
+        <v>-14.4</v>
+      </c>
+      <c r="AJ62" t="n">
+        <v>59.88437866354045</v>
+      </c>
+      <c r="AK62" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AL62" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="AM62" t="inlineStr">
+        <is>
+          <t>Confirmed Accumulation</t>
+        </is>
+      </c>
+      <c r="AN62" t="inlineStr">
+        <is>
+          <t>Confirmed Accumulation</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>14-08-2026</t>
+        </is>
+      </c>
+      <c r="AP62" t="inlineStr">
+        <is>
+          <t>30-09-2026</t>
+        </is>
+      </c>
+      <c r="AQ62" t="n">
+        <v>47</v>
+      </c>
+      <c r="AR62" t="n">
+        <v>62</v>
+      </c>
+      <c r="AS62" t="n">
+        <v>15</v>
+      </c>
+      <c r="AT62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV62" t="n">
         <v>4</v>
       </c>
-      <c r="H62" t="n">
-        <v>0</v>
-      </c>
-      <c r="I62" t="n">
-        <v>184.98</v>
-      </c>
-      <c r="J62" t="n">
-        <v>191.87</v>
-      </c>
-      <c r="K62" t="n">
-        <v>-3.6</v>
-      </c>
-      <c r="L62" t="n">
-        <v>70.02</v>
-      </c>
-      <c r="M62" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="N62" t="n">
-        <v>13430794</v>
-      </c>
-      <c r="O62" t="n">
-        <v>0</v>
-      </c>
-      <c r="P62" t="n">
-        <v>13430794</v>
-      </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
-      <c r="R62" t="inlineStr">
-        <is>
-          <t>Net Buying</t>
-        </is>
-      </c>
-      <c r="S62" t="b">
-        <v>0</v>
-      </c>
-      <c r="T62" t="n">
-        <v>3</v>
-      </c>
-      <c r="U62" t="inlineStr">
-        <is>
-          <t>02-09-2026</t>
-        </is>
-      </c>
-      <c r="V62" t="n">
-        <v>0.041</v>
-      </c>
-      <c r="W62" t="n">
-        <v>3247</v>
-      </c>
-      <c r="X62" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="Y62" t="n">
-        <v>-4</v>
-      </c>
-      <c r="Z62" t="n">
-        <v>51</v>
-      </c>
-      <c r="AA62" t="n">
-        <v>-9</v>
-      </c>
-      <c r="AB62" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AC62" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="AD62" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="AE62" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF62" t="n">
-        <v>21</v>
-      </c>
-      <c r="AG62" t="n">
-        <v>197.92</v>
-      </c>
-      <c r="AH62" t="n">
-        <v>192.7</v>
-      </c>
-      <c r="AI62" t="n">
-        <v>-7.1</v>
-      </c>
-      <c r="AJ62" t="n">
-        <v>191.8684857142857</v>
-      </c>
-      <c r="AK62" t="n">
-        <v>-3.6</v>
-      </c>
-      <c r="AL62" t="inlineStr">
-        <is>
-          <t>Aging</t>
-        </is>
-      </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>Mature Accumulation</t>
-        </is>
-      </c>
-      <c r="AN62" t="inlineStr">
-        <is>
-          <t>Mature — Wait for Pullback</t>
-        </is>
-      </c>
-      <c r="AO62" t="inlineStr">
-        <is>
-          <t>31-08-2026</t>
-        </is>
-      </c>
-      <c r="AP62" t="inlineStr">
-        <is>
-          <t>02-09-2026</t>
-        </is>
-      </c>
-      <c r="AQ62" t="n">
-        <v>2</v>
-      </c>
-      <c r="AR62" t="n">
-        <v>45</v>
-      </c>
-      <c r="AS62" t="n">
-        <v>43</v>
-      </c>
-      <c r="AT62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV62" t="n">
-        <v>0</v>
-      </c>
       <c r="AW62" t="n">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="AX62" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="AY62" t="n">
         <v>0</v>
@@ -14908,13 +14908,13 @@
         <v>0</v>
       </c>
       <c r="BA62" t="n">
-        <v>0</v>
+        <v>2503510</v>
       </c>
       <c r="BB62" t="n">
-        <v>13430794</v>
+        <v>13399767</v>
       </c>
       <c r="BC62" t="n">
-        <v>13430794</v>
+        <v>14302785</v>
       </c>
       <c r="BD62" t="n">
         <v>0</v>
@@ -14950,10 +14950,10 @@
         <v>0</v>
       </c>
       <c r="BO62" t="n">
-        <v>0</v>
+        <v>2503510</v>
       </c>
       <c r="BP62" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="BQ62" t="n">
         <v>0</v>
@@ -14965,12 +14965,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>FOCUS</t>
+          <t>EIEL</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Focus Lighting And Fixtures Limited</t>
+          <t>ENVIRO INFRA ENGINEERS LIMITED</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -14982,40 +14982,40 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F63" t="n">
+        <v>1</v>
+      </c>
+      <c r="G63" t="n">
         <v>4</v>
       </c>
-      <c r="G63" t="n">
-        <v>0</v>
-      </c>
       <c r="H63" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>58.37</v>
+        <v>184.98</v>
       </c>
       <c r="J63" t="n">
-        <v>64.68000000000001</v>
+        <v>191.87</v>
       </c>
       <c r="K63" t="n">
-        <v>-9.800000000000001</v>
+        <v>-3.6</v>
       </c>
       <c r="L63" t="n">
-        <v>56.09</v>
+        <v>70.02</v>
       </c>
       <c r="M63" t="n">
-        <v>1.18</v>
+        <v>1.34</v>
       </c>
       <c r="N63" t="n">
-        <v>11750494</v>
+        <v>13430794</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
       </c>
       <c r="P63" t="n">
-        <v>11750494</v>
+        <v>13430794</v>
       </c>
       <c r="Q63" t="n">
         <v>0</v>
@@ -15029,60 +15029,60 @@
         <v>0</v>
       </c>
       <c r="T63" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>11-09-2026</t>
+          <t>02-09-2026</t>
         </is>
       </c>
       <c r="V63" t="n">
-        <v>0.298</v>
+        <v>0.04</v>
       </c>
       <c r="W63" t="n">
-        <v>394</v>
+        <v>3336</v>
       </c>
       <c r="X63" t="n">
-        <v>64.2</v>
+        <v>19.8</v>
       </c>
       <c r="Y63" t="n">
-        <v>13</v>
+        <v>-4</v>
       </c>
       <c r="Z63" t="n">
-        <v>6.15</v>
+        <v>51</v>
       </c>
       <c r="AA63" t="n">
-        <v>-54</v>
+        <v>-9</v>
       </c>
       <c r="AB63" t="n">
-        <v>0.42</v>
+        <v>2.04</v>
       </c>
       <c r="AC63" t="n">
-        <v>6.55</v>
+        <v>20.8</v>
       </c>
       <c r="AD63" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="AE63" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF63" t="n">
-        <v>13.36</v>
+        <v>21</v>
       </c>
       <c r="AG63" t="n">
-        <v>62.59</v>
+        <v>197.92</v>
       </c>
       <c r="AH63" t="n">
-        <v>72.51000000000001</v>
+        <v>192.7</v>
       </c>
       <c r="AI63" t="n">
-        <v>-13.3</v>
+        <v>-7.1</v>
       </c>
       <c r="AJ63" t="n">
-        <v>64.68221176341068</v>
+        <v>191.8684857142857</v>
       </c>
       <c r="AK63" t="n">
-        <v>-9.800000000000001</v>
+        <v>-3.6</v>
       </c>
       <c r="AL63" t="inlineStr">
         <is>
@@ -15101,22 +15101,22 @@
       </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>27-08-2026</t>
+          <t>31-08-2026</t>
         </is>
       </c>
       <c r="AP63" t="inlineStr">
         <is>
-          <t>11-09-2026</t>
+          <t>02-09-2026</t>
         </is>
       </c>
       <c r="AQ63" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="AR63" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="AS63" t="n">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="AT63" t="n">
         <v>0</v>
@@ -15128,10 +15128,10 @@
         <v>0</v>
       </c>
       <c r="AW63" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AX63" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AY63" t="n">
         <v>0</v>
@@ -15143,10 +15143,10 @@
         <v>0</v>
       </c>
       <c r="BB63" t="n">
-        <v>11750494</v>
+        <v>13430794</v>
       </c>
       <c r="BC63" t="n">
-        <v>11750494</v>
+        <v>13430794</v>
       </c>
       <c r="BD63" t="n">
         <v>0</v>
@@ -15185,7 +15185,7 @@
         <v>0</v>
       </c>
       <c r="BP63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BQ63" t="n">
         <v>0</v>
@@ -15272,10 +15272,10 @@
         <v>0</v>
       </c>
       <c r="W64" t="n">
-        <v>5297</v>
+        <v>4994</v>
       </c>
       <c r="X64" t="n">
-        <v>12.4</v>
+        <v>11.7</v>
       </c>
       <c r="Y64" t="n">
         <v>26</v>
@@ -15501,13 +15501,13 @@
         </is>
       </c>
       <c r="V65" t="n">
-        <v>0.105</v>
+        <v>0.106</v>
       </c>
       <c r="W65" t="n">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="X65" t="n">
-        <v>7.63</v>
+        <v>7.54</v>
       </c>
       <c r="Y65" t="n">
         <v>118</v>
@@ -15729,13 +15729,13 @@
         </is>
       </c>
       <c r="V66" t="n">
-        <v>0.147</v>
+        <v>0.145</v>
       </c>
       <c r="W66" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="X66" t="n">
-        <v>31.6</v>
+        <v>32</v>
       </c>
       <c r="Y66" t="n">
         <v>19</v>
@@ -15961,10 +15961,10 @@
         </is>
       </c>
       <c r="V67" t="n">
-        <v>0.011</v>
+        <v>0.012</v>
       </c>
       <c r="W67" t="n">
-        <v>3903</v>
+        <v>3855</v>
       </c>
       <c r="X67" t="inlineStr"/>
       <c r="Y67" t="n">
@@ -16191,13 +16191,13 @@
         </is>
       </c>
       <c r="V68" t="n">
-        <v>0.076</v>
+        <v>0.078</v>
       </c>
       <c r="W68" t="n">
-        <v>447</v>
+        <v>431</v>
       </c>
       <c r="X68" t="n">
-        <v>13.2</v>
+        <v>12.7</v>
       </c>
       <c r="Y68" t="n">
         <v>-8</v>
@@ -16360,7 +16360,7 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -16368,7 +16368,7 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F69" t="n">
         <v>8</v>
@@ -16426,10 +16426,10 @@
         <v>0.1</v>
       </c>
       <c r="W69" t="n">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="X69" t="n">
-        <v>27.4</v>
+        <v>27.5</v>
       </c>
       <c r="Y69" t="n">
         <v>24</v>
@@ -16655,13 +16655,13 @@
         </is>
       </c>
       <c r="V70" t="n">
-        <v>0.034</v>
+        <v>0.033</v>
       </c>
       <c r="W70" t="n">
-        <v>1442</v>
+        <v>1480</v>
       </c>
       <c r="X70" t="n">
-        <v>25.2</v>
+        <v>25.9</v>
       </c>
       <c r="Y70" t="n">
         <v>11</v>
@@ -16890,10 +16890,10 @@
         <v>0</v>
       </c>
       <c r="W71" t="n">
-        <v>3463</v>
+        <v>3375</v>
       </c>
       <c r="X71" t="n">
-        <v>45.1</v>
+        <v>44</v>
       </c>
       <c r="Y71" t="n">
         <v>5</v>
@@ -17122,10 +17122,10 @@
         <v>0.003</v>
       </c>
       <c r="W72" t="n">
-        <v>12886</v>
+        <v>12789</v>
       </c>
       <c r="X72" t="n">
-        <v>41.1</v>
+        <v>40.8</v>
       </c>
       <c r="Y72" t="n">
         <v>31</v>
@@ -17354,10 +17354,10 @@
         <v>0.03</v>
       </c>
       <c r="W73" t="n">
-        <v>988</v>
+        <v>973</v>
       </c>
       <c r="X73" t="n">
-        <v>20.3</v>
+        <v>20</v>
       </c>
       <c r="Y73" t="n">
         <v>27</v>
@@ -17586,7 +17586,7 @@
         <v>0.053</v>
       </c>
       <c r="W74" t="n">
-        <v>934</v>
+        <v>929</v>
       </c>
       <c r="X74" t="inlineStr"/>
       <c r="Y74" t="n">
@@ -17816,10 +17816,10 @@
         <v>0</v>
       </c>
       <c r="W75" t="n">
-        <v>3820</v>
+        <v>3777</v>
       </c>
       <c r="X75" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="Y75" t="n">
         <v>42</v>
@@ -18048,7 +18048,7 @@
         <v>0.006</v>
       </c>
       <c r="W76" t="n">
-        <v>4834</v>
+        <v>4843</v>
       </c>
       <c r="X76" t="n">
         <v>12.5</v>
@@ -18276,10 +18276,10 @@
         <v>0.026</v>
       </c>
       <c r="W77" t="n">
-        <v>1571</v>
+        <v>1545</v>
       </c>
       <c r="X77" t="n">
-        <v>38.2</v>
+        <v>37.5</v>
       </c>
       <c r="Y77" t="inlineStr"/>
       <c r="Z77" t="n">
@@ -18496,10 +18496,10 @@
         <v>0</v>
       </c>
       <c r="W78" t="n">
-        <v>30397</v>
+        <v>30645</v>
       </c>
       <c r="X78" t="n">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Y78" t="n">
         <v>62</v>
@@ -18728,7 +18728,7 @@
         <v>0</v>
       </c>
       <c r="W79" t="n">
-        <v>104987</v>
+        <v>105095</v>
       </c>
       <c r="X79" t="n">
         <v>30.2</v>
@@ -18957,10 +18957,10 @@
         </is>
       </c>
       <c r="V80" t="n">
-        <v>0.355</v>
+        <v>0.358</v>
       </c>
       <c r="W80" t="n">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="X80" t="inlineStr"/>
       <c r="Y80" t="n">
@@ -19187,13 +19187,13 @@
         </is>
       </c>
       <c r="V81" t="n">
-        <v>0.229</v>
+        <v>0.227</v>
       </c>
       <c r="W81" t="n">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="X81" t="n">
-        <v>23.4</v>
+        <v>23.6</v>
       </c>
       <c r="Y81" t="n">
         <v>21</v>
@@ -19419,10 +19419,10 @@
         </is>
       </c>
       <c r="V82" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.083</v>
       </c>
       <c r="W82" t="n">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="X82" t="inlineStr"/>
       <c r="Y82" t="n">
@@ -19929,101 +19929,101 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BMWVENTLTD</t>
+          <t>NURECA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BMW VENTURES LIMITED</t>
+          <t>NURECA LIMITED</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>65.48</v>
+        <v>323.35</v>
       </c>
       <c r="D10" t="n">
-        <v>55.06</v>
+        <v>333.11</v>
       </c>
       <c r="E10" t="n">
-        <v>18.9</v>
+        <v>-2.9</v>
       </c>
       <c r="F10" t="n">
-        <v>73.01000000000001</v>
+        <v>63.24</v>
       </c>
       <c r="G10" t="n">
-        <v>2.9</v>
+        <v>3.75</v>
       </c>
       <c r="H10" t="n">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>22-09-2026</t>
+          <t>30-09-2026</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>NURECA</t>
+          <t>SRHHYPOLTD</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NURECA LIMITED</t>
+          <t>Sree Rayalaseema Hi-Strength Hypo Limited</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>323.35</v>
+        <v>550.6</v>
       </c>
       <c r="D11" t="n">
-        <v>333.11</v>
+        <v>510.94</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.9</v>
+        <v>7.8</v>
       </c>
       <c r="F11" t="n">
-        <v>63.24</v>
+        <v>61.84</v>
       </c>
       <c r="G11" t="n">
-        <v>3.75</v>
+        <v>3.06</v>
       </c>
       <c r="H11" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>21-09-2026</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SRHHYPOLTD</t>
+          <t>SIGIND</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Sree Rayalaseema Hi-Strength Hypo Limited</t>
+          <t>Signet Industries Limited</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>550.6</v>
+        <v>58.31</v>
       </c>
       <c r="D12" t="n">
-        <v>510.94</v>
+        <v>74.22</v>
       </c>
       <c r="E12" t="n">
-        <v>7.8</v>
+        <v>-21.4</v>
       </c>
       <c r="F12" t="n">
-        <v>61.84</v>
+        <v>72.56999999999999</v>
       </c>
       <c r="G12" t="n">
-        <v>3.06</v>
+        <v>2.01</v>
       </c>
       <c r="H12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -20034,70 +20034,70 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SIGIND</t>
+          <t>THANGAMAYL</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Signet Industries Limited</t>
+          <t>THANGAMAYIL JEWELLERY LIMITED</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>58.31</v>
+        <v>4849.5</v>
       </c>
       <c r="D13" t="n">
-        <v>74.22</v>
+        <v>5198.76</v>
       </c>
       <c r="E13" t="n">
-        <v>-21.4</v>
+        <v>-6.7</v>
       </c>
       <c r="F13" t="n">
-        <v>72.56999999999999</v>
+        <v>67.31999999999999</v>
       </c>
       <c r="G13" t="n">
-        <v>2.01</v>
+        <v>7.21</v>
       </c>
       <c r="H13" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>21-09-2026</t>
+          <t>31-08-2026</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>THANGAMAYL</t>
+          <t>BMWVENTLTD</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>THANGAMAYIL JEWELLERY LIMITED</t>
+          <t>BMW VENTURES LIMITED</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>4849.5</v>
+        <v>65.48</v>
       </c>
       <c r="D14" t="n">
-        <v>5198.76</v>
+        <v>55.06</v>
       </c>
       <c r="E14" t="n">
-        <v>-6.7</v>
+        <v>18.9</v>
       </c>
       <c r="F14" t="n">
-        <v>67.31999999999999</v>
+        <v>73.01000000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>7.21</v>
+        <v>2.9</v>
       </c>
       <c r="H14" t="n">
         <v>6</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>31-08-2026</t>
+          <t>22-09-2026</t>
         </is>
       </c>
     </row>
@@ -20804,140 +20804,140 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>GANESHCP</t>
+          <t>HTEL</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>GANESH CONSUMER PRODUCTS LIMITED</t>
+          <t>Hy-Tech Engineers Limited</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>163.82</v>
+        <v>92.93000000000001</v>
       </c>
       <c r="D35" t="n">
-        <v>166</v>
+        <v>68.68000000000001</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.3</v>
+        <v>35.3</v>
       </c>
       <c r="F35" t="n">
-        <v>64.08</v>
+        <v>71.36</v>
       </c>
       <c r="G35" t="n">
-        <v>0.8</v>
+        <v>0.86</v>
       </c>
       <c r="H35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>02-09-2026</t>
+          <t>29-09-2026</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SRGHFL</t>
+          <t>GANESHCP</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SRG HOUSING FINANCE LIMITED</t>
+          <t>GANESH CONSUMER PRODUCTS LIMITED</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>112.2</v>
+        <v>163.82</v>
       </c>
       <c r="D36" t="n">
-        <v>132.2</v>
+        <v>166</v>
       </c>
       <c r="E36" t="n">
-        <v>-15.1</v>
+        <v>-1.3</v>
       </c>
       <c r="F36" t="n">
-        <v>67.83</v>
+        <v>64.08</v>
       </c>
       <c r="G36" t="n">
-        <v>1.98</v>
+        <v>0.8</v>
       </c>
       <c r="H36" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>16-09-2026</t>
+          <t>02-09-2026</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>HTEL</t>
+          <t>GREENPANEL</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Hy-Tech Engineers Limited</t>
+          <t>Greenpanel Industries Limited</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>92.93000000000001</v>
+        <v>147.83</v>
       </c>
       <c r="D37" t="n">
-        <v>68.68000000000001</v>
+        <v>155.33</v>
       </c>
       <c r="E37" t="n">
-        <v>35.3</v>
+        <v>-4.8</v>
       </c>
       <c r="F37" t="n">
-        <v>71.36</v>
+        <v>53.12</v>
       </c>
       <c r="G37" t="n">
-        <v>0.86</v>
+        <v>19.88</v>
       </c>
       <c r="H37" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>29-09-2026</t>
+          <t>18-09-2026</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>GREENPANEL</t>
+          <t>SRGHFL</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Greenpanel Industries Limited</t>
+          <t>SRG HOUSING FINANCE LIMITED</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>147.83</v>
+        <v>112.2</v>
       </c>
       <c r="D38" t="n">
-        <v>155.33</v>
+        <v>132.2</v>
       </c>
       <c r="E38" t="n">
-        <v>-4.8</v>
+        <v>-15.1</v>
       </c>
       <c r="F38" t="n">
-        <v>53.12</v>
+        <v>67.83</v>
       </c>
       <c r="G38" t="n">
-        <v>19.88</v>
+        <v>1.98</v>
       </c>
       <c r="H38" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>18-09-2026</t>
+          <t>16-09-2026</t>
         </is>
       </c>
     </row>
@@ -21574,245 +21574,245 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>PAISALO</t>
+          <t>FOCUS</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>PAISALO DIGITAL LIMITED</t>
+          <t>Focus Lighting And Fixtures Limited</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>81.70999999999999</v>
+        <v>58.37</v>
       </c>
       <c r="D57" t="n">
-        <v>93.86</v>
+        <v>64.68000000000001</v>
       </c>
       <c r="E57" t="n">
-        <v>-12.9</v>
+        <v>-9.800000000000001</v>
       </c>
       <c r="F57" t="n">
-        <v>50.38</v>
+        <v>56.09</v>
       </c>
       <c r="G57" t="n">
-        <v>2.16</v>
+        <v>1.18</v>
       </c>
       <c r="H57" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>22-09-2026</t>
+          <t>11-09-2026</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>RAMASTEEL</t>
+          <t>PAISALO</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Rama Steel Tubes Limited</t>
+          <t>PAISALO DIGITAL LIMITED</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>4.01</v>
+        <v>81.70999999999999</v>
       </c>
       <c r="D58" t="n">
-        <v>4.45</v>
+        <v>93.86</v>
       </c>
       <c r="E58" t="n">
-        <v>-9.9</v>
+        <v>-12.9</v>
       </c>
       <c r="F58" t="n">
-        <v>57.22</v>
+        <v>50.38</v>
       </c>
       <c r="G58" t="n">
-        <v>3.87</v>
+        <v>2.16</v>
       </c>
       <c r="H58" t="n">
         <v>2</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>22-09-2026</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>LINC</t>
+          <t>RAMASTEEL</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>LINC LIMITED</t>
+          <t>Rama Steel Tubes Limited</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>85.16</v>
+        <v>4.01</v>
       </c>
       <c r="D59" t="n">
-        <v>91.15000000000001</v>
+        <v>4.45</v>
       </c>
       <c r="E59" t="n">
-        <v>-6.6</v>
+        <v>-9.9</v>
       </c>
       <c r="F59" t="n">
-        <v>59.44</v>
+        <v>57.22</v>
       </c>
       <c r="G59" t="n">
-        <v>2.28</v>
+        <v>3.87</v>
       </c>
       <c r="H59" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>29-09-2026</t>
+          <t>30-09-2026</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>LIBERTSHOE</t>
+          <t>LINC</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>LIBERTY SHOES LIMITED</t>
+          <t>LINC LIMITED</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>209.08</v>
+        <v>85.16</v>
       </c>
       <c r="D60" t="n">
-        <v>244.24</v>
+        <v>91.15000000000001</v>
       </c>
       <c r="E60" t="n">
-        <v>-14.4</v>
+        <v>-6.6</v>
       </c>
       <c r="F60" t="n">
-        <v>58.5</v>
+        <v>59.44</v>
       </c>
       <c r="G60" t="n">
-        <v>1.71</v>
+        <v>2.28</v>
       </c>
       <c r="H60" t="n">
         <v>5</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>19-08-2026</t>
+          <t>29-09-2026</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>WSI</t>
+          <t>LIBERTSHOE</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>W S Industries (I) Limited</t>
+          <t>LIBERTY SHOES LIMITED</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>63.86</v>
+        <v>209.08</v>
       </c>
       <c r="D61" t="n">
-        <v>59.88</v>
+        <v>244.24</v>
       </c>
       <c r="E61" t="n">
-        <v>6.6</v>
+        <v>-14.4</v>
       </c>
       <c r="F61" t="n">
-        <v>57.6</v>
+        <v>58.5</v>
       </c>
       <c r="G61" t="n">
-        <v>1.43</v>
+        <v>1.71</v>
       </c>
       <c r="H61" t="n">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>19-08-2026</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>EIEL</t>
+          <t>WSI</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>ENVIRO INFRA ENGINEERS LIMITED</t>
+          <t>W S Industries (I) Limited</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>184.98</v>
+        <v>63.86</v>
       </c>
       <c r="D62" t="n">
-        <v>191.87</v>
+        <v>59.88</v>
       </c>
       <c r="E62" t="n">
-        <v>-3.6</v>
+        <v>6.6</v>
       </c>
       <c r="F62" t="n">
-        <v>70.02</v>
+        <v>57.6</v>
       </c>
       <c r="G62" t="n">
-        <v>1.34</v>
+        <v>1.43</v>
       </c>
       <c r="H62" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>02-09-2026</t>
+          <t>30-09-2026</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>FOCUS</t>
+          <t>EIEL</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Focus Lighting And Fixtures Limited</t>
+          <t>ENVIRO INFRA ENGINEERS LIMITED</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>58.37</v>
+        <v>184.98</v>
       </c>
       <c r="D63" t="n">
-        <v>64.68000000000001</v>
+        <v>191.87</v>
       </c>
       <c r="E63" t="n">
-        <v>-9.800000000000001</v>
+        <v>-3.6</v>
       </c>
       <c r="F63" t="n">
-        <v>56.09</v>
+        <v>70.02</v>
       </c>
       <c r="G63" t="n">
-        <v>1.18</v>
+        <v>1.34</v>
       </c>
       <c r="H63" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>11-09-2026</t>
+          <t>02-09-2026</t>
         </is>
       </c>
     </row>
